--- a/compras-proyecto.xlsx
+++ b/compras-proyecto.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="Rb3cf6cb0595742d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="2" r:id="R9f55693a104b43ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Láminas" sheetId="3" r:id="Rf5fef9e5deff44b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="4" r:id="R5736bd6e5b5c4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="5" r:id="R2332c494379743bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloqueos" sheetId="6" r:id="R26475d8f3f5140dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En el armado" sheetId="7" r:id="Rc249f97e798842ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="R22261d597eb64c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="2" r:id="R1aee4edc6ec641ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Láminas" sheetId="3" r:id="R5cdc49ae4d094ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="4" r:id="R9f55a881f64e4ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="5" r:id="R89e54929ecef4b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloqueos" sheetId="6" r:id="Rd41c2da8a27c4626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En el armado" sheetId="7" r:id="R87b8fa41abe74842"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -405,7 +405,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Estimación conjunta del 27/10/2026, generada desde los Excel de cada mueble (herramientas/build_compras_proyecto.py).</x:v>
+        <x:v>Estimación conjunta del 28/10/2026, generada desde los Excel de cada mueble (herramientas/build_compras_proyecto.py).</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -427,13 +427,13 @@
         <x:v>Láminas RH15</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="13" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>Cocina 4 + clóset 5 + baño 1 por separado; encaje conjunto en la hoja Láminas.</x:v>
+        <x:v>Cocina 4 + clóset 4 + baño 1 por separado; encaje conjunto en la hoja Láminas.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -475,7 +475,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="13" t="str">
-        <x:v>Sobran unos 28 m para cantear piezas pequeñas en el armado.</x:v>
+        <x:v>Sobran unos 19 m para cantear piezas pequeñas en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -753,7 +753,7 @@
         <v>150 × 99,1</v>
       </c>
       <c r="P9" s="17" t="str">
-        <v>Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         <v>570 × 99,55</v>
       </c>
       <c r="P14" s="17" t="str">
-        <v>Si no la cantean: cortar a 570 × 99.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 570 × 99,55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="15" ht="28.799999237060547">
@@ -1103,7 +1103,7 @@
         <v>570 × 79,55</v>
       </c>
       <c r="P16" s="17" t="str">
-        <v>Si no la cantean: cortar a 570 × 79.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 570 × 79,55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="17" ht="43.20000076293945">
@@ -1303,7 +1303,7 @@
         <v>640 × 99,1</v>
       </c>
       <c r="P20" s="17" t="str">
-        <v>Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="21">
@@ -1503,7 +1503,7 @@
         <v>549,55 × 74,55</v>
       </c>
       <c r="P24" s="17" t="str">
-        <v>Si no la cantean: cortar a 549.55 × 74.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 549,55 × 74,55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="25">
@@ -1553,7 +1553,7 @@
         <v>583 × 74,55</v>
       </c>
       <c r="P25" s="17" t="str">
-        <v>Si no la cantean: cortar a 583 × 74.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 583 × 74,55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="26">
@@ -1853,7 +1853,7 @@
         <v>669,1 × 99,1</v>
       </c>
       <c r="P31" s="17" t="str">
-        <v>Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="32">
@@ -2203,7 +2203,7 @@
         <v>370 × 99,1</v>
       </c>
       <c r="P38" s="17" t="str">
-        <v>Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="39">
@@ -2503,7 +2503,7 @@
         <v>1274,1 × 96,1</v>
       </c>
       <c r="P44" s="17" t="str">
-        <v>Si no la cantean: cortar a 1274.1 × 96.1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 1274,1 × 96,1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="45">
@@ -3103,7 +3103,7 @@
         <v>569,1 × 59,1</v>
       </c>
       <c r="P56" s="17" t="str">
-        <v>Si no la cantean: cortar a 569.1 × 59.1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</v>
+        <v>Si no la cantean: cortar a 569,1 × 59,1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</v>
       </c>
     </row>
     <row r="57">
@@ -3447,7 +3447,7 @@
         <v>Normal</v>
       </c>
       <c r="N63" s="16" t="str">
-        <v>717 × 324.5</v>
+        <v>717 × 324,5</v>
       </c>
       <c r="O63" s="16" t="str">
         <v>713 × 320,5</v>
@@ -3497,7 +3497,7 @@
         <v>Normal</v>
       </c>
       <c r="N64" s="16" t="str">
-        <v>717 × 324.5</v>
+        <v>717 × 324,5</v>
       </c>
       <c r="O64" s="16" t="str">
         <v>713 × 320,5</v>
@@ -3653,7 +3653,7 @@
         <v>684,1 × 59,1</v>
       </c>
       <c r="P67" s="17" t="str">
-        <v>Si no la cantean: cortar a 684.1 × 59.1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 684,1 × 59,1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="68">
@@ -3703,7 +3703,7 @@
         <v>684,1 × 79,1</v>
       </c>
       <c r="P68" s="17" t="str">
-        <v>Si no la cantean: cortar a 684.1 × 79.1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 684,1 × 79,1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="69">
@@ -3797,7 +3797,7 @@
         <v>Normal</v>
       </c>
       <c r="N70" s="16" t="str">
-        <v>717 × 354.5</v>
+        <v>717 × 354,5</v>
       </c>
       <c r="O70" s="16" t="str">
         <v>713 × 350,5</v>
@@ -3847,7 +3847,7 @@
         <v>Normal</v>
       </c>
       <c r="N71" s="16" t="str">
-        <v>717 × 354.5</v>
+        <v>717 × 354,5</v>
       </c>
       <c r="O71" s="16" t="str">
         <v>713 × 350,5</v>
@@ -4361,13 +4361,13 @@
         <v>Clóset</v>
       </c>
       <c r="B82" s="16" t="str">
-        <v>C3-005</v>
+        <v>C3-025</v>
       </c>
       <c r="C82" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D82" s="17" t="str">
-        <v>Fondo RH15</v>
+        <v>Amarre posterior superior izquierdo</v>
       </c>
       <c r="E82" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4376,13 +4376,13 @@
         <v>1</v>
       </c>
       <c r="G82" s="16" t="n">
-        <v>2250</v>
+        <v>830</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>830</v>
+        <v>100</v>
       </c>
       <c r="I82" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="J82" s="16" t="str">
         <v>—</v>
@@ -4394,16 +4394,16 @@
         <v>—</v>
       </c>
       <c r="M82" s="16" t="str">
-        <v>Sin canto</v>
+        <v>Pequeña</v>
       </c>
       <c r="N82" s="16" t="str">
-        <v>2250 × 830</v>
+        <v>830 × 100</v>
       </c>
       <c r="O82" s="16" t="str">
-        <v>2250 × 830</v>
+        <v>830 × 99,55</v>
       </c>
       <c r="P82" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="83">
@@ -4661,13 +4661,13 @@
         <v>Clóset</v>
       </c>
       <c r="B88" s="16" t="str">
-        <v>C3-011</v>
+        <v>C3-026</v>
       </c>
       <c r="C88" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D88" s="17" t="str">
-        <v>Fondo RH15</v>
+        <v>Amarre posterior superior derecho</v>
       </c>
       <c r="E88" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4676,13 +4676,13 @@
         <v>1</v>
       </c>
       <c r="G88" s="16" t="n">
-        <v>2250</v>
+        <v>1075</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>1075</v>
+        <v>100</v>
       </c>
       <c r="I88" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="J88" s="16" t="str">
         <v>—</v>
@@ -4694,16 +4694,16 @@
         <v>—</v>
       </c>
       <c r="M88" s="16" t="str">
-        <v>Sin canto</v>
+        <v>Pequeña</v>
       </c>
       <c r="N88" s="16" t="str">
-        <v>2250 × 1075</v>
+        <v>1075 × 100</v>
       </c>
       <c r="O88" s="16" t="str">
-        <v>2250 × 1075</v>
+        <v>1075 × 99,55</v>
       </c>
       <c r="P88" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="89">
@@ -5358,202 +5358,202 @@
     </row>
     <row r="102" ht="28.799999237060547">
       <c r="A102" s="16" t="str">
-        <v>Baño</v>
+        <v>Clóset</v>
       </c>
       <c r="B102" s="16" t="str">
-        <v>B01</v>
+        <v>C3-027</v>
       </c>
       <c r="C102" s="16" t="str">
-        <v>BAJO</v>
+        <v>B2</v>
       </c>
       <c r="D102" s="17" t="str">
-        <v>Lateral</v>
+        <v>Montante posterior derecho</v>
       </c>
       <c r="E102" s="16" t="str">
-        <v>RH15 Cartagena</v>
+        <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F102" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="16" t="n">
-        <v>470</v>
+        <v>2050</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="I102" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J102" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K102" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L102" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M102" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N102" s="16" t="str">
-        <v>470 × 450</v>
+        <v>2050 × 100</v>
       </c>
       <c r="O102" s="16" t="str">
-        <v>469,1 × 449,1</v>
+        <v>2050 × 99,55</v>
       </c>
       <c r="P102" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="103" ht="28.799999237060547">
       <c r="A103" s="16" t="str">
-        <v>Baño</v>
+        <v>Clóset</v>
       </c>
       <c r="B103" s="16" t="str">
-        <v>B02</v>
+        <v>C3-028</v>
       </c>
       <c r="C103" s="16" t="str">
-        <v>BAJO</v>
+        <v>B1</v>
       </c>
       <c r="D103" s="17" t="str">
-        <v>Piso</v>
+        <v>Montante posterior izquierdo</v>
       </c>
       <c r="E103" s="16" t="str">
-        <v>RH15 Cartagena</v>
+        <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F103" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="16" t="n">
-        <v>490</v>
+        <v>2050</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="I103" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J103" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K103" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L103" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M103" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N103" s="16" t="str">
-        <v>490 × 450</v>
+        <v>2050 × 100</v>
       </c>
       <c r="O103" s="16" t="str">
-        <v>489,1 × 449,1</v>
+        <v>2050 × 99,55</v>
       </c>
       <c r="P103" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="104" ht="57.599998474121094">
       <c r="A104" s="16" t="str">
-        <v>Baño</v>
+        <v>Clóset</v>
       </c>
       <c r="B104" s="16" t="str">
-        <v>B03</v>
+        <v>C3-029</v>
       </c>
       <c r="C104" s="16" t="str">
-        <v>BAJO</v>
+        <v>B1</v>
       </c>
       <c r="D104" s="17" t="str">
-        <v>Entrepaño retranqueado con reserva de sifón</v>
+        <v>Amarre posterior inferior izquierdo</v>
       </c>
       <c r="E104" s="16" t="str">
-        <v>RH15 Cartagena</v>
+        <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F104" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="16" t="n">
-        <v>490</v>
+        <v>830</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>405</v>
+        <v>100</v>
       </c>
       <c r="I104" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J104" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K104" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L104" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M104" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N104" s="16" t="str">
-        <v>490 × 405</v>
+        <v>830 × 100</v>
       </c>
       <c r="O104" s="16" t="str">
-        <v>489,1 × 404,1</v>
+        <v>830 × 99,55</v>
       </c>
       <c r="P104" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="105" ht="57.599998474121094">
       <c r="A105" s="16" t="str">
-        <v>Baño</v>
+        <v>Clóset</v>
       </c>
       <c r="B105" s="16" t="str">
-        <v>B04</v>
+        <v>C3-030</v>
       </c>
       <c r="C105" s="16" t="str">
-        <v>BAJO</v>
+        <v>B2</v>
       </c>
       <c r="D105" s="17" t="str">
-        <v>Travesaño trasero superior lateral</v>
+        <v>Amarre posterior inferior derecho</v>
       </c>
       <c r="E105" s="16" t="str">
-        <v>RH15 Cartagena</v>
+        <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" s="16" t="n">
-        <v>195</v>
+        <v>1075</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I105" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J105" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K105" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L105" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M105" s="16" t="str">
         <v>Pequeña</v>
       </c>
       <c r="N105" s="16" t="str">
-        <v>195 × 80</v>
+        <v>1075 × 100</v>
       </c>
       <c r="O105" s="16" t="str">
-        <v>194,1 × 79,1</v>
+        <v>1075 × 99,55</v>
       </c>
       <c r="P105" s="17" t="str">
-        <v>Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="106" ht="57.599998474121094">
@@ -5561,25 +5561,25 @@
         <v>Baño</v>
       </c>
       <c r="B106" s="16" t="str">
-        <v>B05</v>
+        <v>B01</v>
       </c>
       <c r="C106" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D106" s="17" t="str">
-        <v>Travesaño trasero inferior</v>
+        <v>Lateral</v>
       </c>
       <c r="E106" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F106" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" s="16" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="I106" s="16" t="str">
         <v>F</v>
@@ -5594,16 +5594,16 @@
         <v>F</v>
       </c>
       <c r="M106" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N106" s="16" t="str">
-        <v>490 × 80</v>
+        <v>470 × 450</v>
       </c>
       <c r="O106" s="16" t="str">
-        <v>489,1 × 79,1</v>
+        <v>469,1 × 449,1</v>
       </c>
       <c r="P106" s="17" t="str">
-        <v>Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="107" ht="100.80000305175781">
@@ -5611,13 +5611,13 @@
         <v>Baño</v>
       </c>
       <c r="B107" s="16" t="str">
-        <v>B06</v>
+        <v>B02</v>
       </c>
       <c r="C107" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D107" s="17" t="str">
-        <v>Panel común para dos puertas: corte diagonal en armado</v>
+        <v>Piso</v>
       </c>
       <c r="E107" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5626,34 +5626,34 @@
         <v>1</v>
       </c>
       <c r="G107" s="16" t="n">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="I107" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J107" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="K107" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L107" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M107" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N107" s="16" t="str">
-        <v>299 × 517</v>
+        <v>490 × 450</v>
       </c>
       <c r="O107" s="16" t="str">
-        <v>295 × 513</v>
+        <v>489,1 × 449,1</v>
       </c>
       <c r="P107" s="17" t="str">
-        <v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</v>
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="108" ht="43.20000076293945">
@@ -5661,25 +5661,25 @@
         <v>Baño</v>
       </c>
       <c r="B108" s="16" t="str">
-        <v>S01</v>
+        <v>B03</v>
       </c>
       <c r="C108" s="16" t="str">
-        <v>ESPEJO</v>
+        <v>BAJO</v>
       </c>
       <c r="D108" s="17" t="str">
-        <v>Lateral gabinete superior</v>
+        <v>Entrepaño retranqueado con reserva de sifón</v>
       </c>
       <c r="E108" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F108" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" s="16" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>105</v>
+        <v>405</v>
       </c>
       <c r="I108" s="16" t="str">
         <v>F</v>
@@ -5697,13 +5697,13 @@
         <v>Normal</v>
       </c>
       <c r="N108" s="16" t="str">
-        <v>500 × 105</v>
+        <v>490 × 405</v>
       </c>
       <c r="O108" s="16" t="str">
-        <v>499,1 × 104,1</v>
+        <v>489,1 × 404,1</v>
       </c>
       <c r="P108" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="109" ht="28.799999237060547">
@@ -5711,13 +5711,13 @@
         <v>Baño</v>
       </c>
       <c r="B109" s="16" t="str">
-        <v>S02</v>
+        <v>B04</v>
       </c>
       <c r="C109" s="16" t="str">
-        <v>ESPEJO</v>
+        <v>BAJO</v>
       </c>
       <c r="D109" s="17" t="str">
-        <v>Piso y techo gabinete superior</v>
+        <v>Travesaño trasero superior lateral</v>
       </c>
       <c r="E109" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5726,10 +5726,10 @@
         <v>2</v>
       </c>
       <c r="G109" s="16" t="n">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="I109" s="16" t="str">
         <v>F</v>
@@ -5744,16 +5744,16 @@
         <v>F</v>
       </c>
       <c r="M109" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N109" s="16" t="str">
-        <v>420 × 105</v>
+        <v>195 × 80</v>
       </c>
       <c r="O109" s="16" t="str">
-        <v>419,1 × 104,1</v>
+        <v>194,1 × 79,1</v>
       </c>
       <c r="P109" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="110" ht="43.20000076293945">
@@ -5761,13 +5761,13 @@
         <v>Baño</v>
       </c>
       <c r="B110" s="16" t="str">
-        <v>S03</v>
+        <v>B05</v>
       </c>
       <c r="C110" s="16" t="str">
-        <v>ESPEJO</v>
+        <v>BAJO</v>
       </c>
       <c r="D110" s="17" t="str">
-        <v>División vertical</v>
+        <v>Travesaño trasero inferior</v>
       </c>
       <c r="E110" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5776,10 +5776,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="16" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="I110" s="16" t="str">
         <v>F</v>
@@ -5794,16 +5794,16 @@
         <v>F</v>
       </c>
       <c r="M110" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N110" s="16" t="str">
-        <v>470 × 105</v>
+        <v>490 × 80</v>
       </c>
       <c r="O110" s="16" t="str">
-        <v>469,1 × 104,1</v>
+        <v>489,1 × 79,1</v>
       </c>
       <c r="P110" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="111" ht="43.20000076293945">
@@ -5811,49 +5811,49 @@
         <v>Baño</v>
       </c>
       <c r="B111" s="16" t="str">
-        <v>S04</v>
+        <v>B06</v>
       </c>
       <c r="C111" s="16" t="str">
-        <v>ESPEJO</v>
+        <v>BAJO</v>
       </c>
       <c r="D111" s="17" t="str">
-        <v>Entrepaño interior izquierdo</v>
+        <v>Panel común para dos puertas: corte diagonal en armado</v>
       </c>
       <c r="E111" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" s="16" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="H111" s="16" t="n">
-        <v>100</v>
+        <v>517</v>
       </c>
       <c r="I111" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J111" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="K111" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="L111" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="M111" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N111" s="16" t="str">
-        <v>290 × 100</v>
+        <v>299 × 517</v>
       </c>
       <c r="O111" s="16" t="str">
-        <v>289,1 × 99,1</v>
+        <v>295 × 513</v>
       </c>
       <c r="P111" s="17" t="str">
-        <v>Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</v>
       </c>
     </row>
     <row r="112" ht="43.20000076293945">
@@ -5861,25 +5861,25 @@
         <v>Baño</v>
       </c>
       <c r="B112" s="16" t="str">
-        <v>S05</v>
+        <v>S01</v>
       </c>
       <c r="C112" s="16" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D112" s="17" t="str">
-        <v>Entrepaño columna abierta derecha</v>
+        <v>Lateral gabinete superior</v>
       </c>
       <c r="E112" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F112" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" s="16" t="n">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I112" s="16" t="str">
         <v>F</v>
@@ -5894,16 +5894,16 @@
         <v>F</v>
       </c>
       <c r="M112" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N112" s="16" t="str">
-        <v>115 × 100</v>
+        <v>500 × 105</v>
       </c>
       <c r="O112" s="16" t="str">
-        <v>114,1 × 99,1</v>
+        <v>499,1 × 104,1</v>
       </c>
       <c r="P112" s="17" t="str">
-        <v>Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="113" ht="43.20000076293945">
@@ -5911,25 +5911,25 @@
         <v>Baño</v>
       </c>
       <c r="B113" s="16" t="str">
-        <v>S06</v>
+        <v>S02</v>
       </c>
       <c r="C113" s="16" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D113" s="17" t="str">
-        <v>Tapa RH15 portadora del espejo</v>
+        <v>Piso y techo gabinete superior</v>
       </c>
       <c r="E113" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F113" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113" s="16" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>320</v>
+        <v>105</v>
       </c>
       <c r="I113" s="16" t="str">
         <v>F</v>
@@ -5947,13 +5947,13 @@
         <v>Normal</v>
       </c>
       <c r="N113" s="16" t="str">
-        <v>500 × 320</v>
+        <v>420 × 105</v>
       </c>
       <c r="O113" s="16" t="str">
-        <v>499,1 × 319,1</v>
+        <v>419,1 × 104,1</v>
       </c>
       <c r="P113" s="17" t="str">
-        <v>Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="114" ht="43.20000076293945">
@@ -5961,25 +5961,25 @@
         <v>Baño</v>
       </c>
       <c r="B114" s="16" t="str">
-        <v>F01</v>
+        <v>S03</v>
       </c>
       <c r="C114" s="16" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D114" s="17" t="str">
-        <v>Fondo blanco de 6 mm</v>
+        <v>División vertical</v>
       </c>
       <c r="E114" s="16" t="str">
-        <v>Fondo melamina blanco RH6</v>
+        <v>RH15 Cartagena</v>
       </c>
       <c r="F114" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="16" t="n">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>446</v>
+        <v>105</v>
       </c>
       <c r="I114" s="16" t="str">
         <v>F</v>
@@ -5997,17 +5997,217 @@
         <v>Normal</v>
       </c>
       <c r="N114" s="16" t="str">
+        <v>470 × 105</v>
+      </c>
+      <c r="O114" s="16" t="str">
+        <v>469,1 × 104,1</v>
+      </c>
+      <c r="P114" s="17" t="str">
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B115" s="13" t="str">
+        <v>S04</v>
+      </c>
+      <c r="C115" s="13" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D115" s="13" t="str">
+        <v>Entrepaño interior izquierdo</v>
+      </c>
+      <c r="E115" s="13" t="str">
+        <v>RH15 Cartagena</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="H115" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I115" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="J115" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="K115" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="L115" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="M115" s="13" t="str">
+        <v>Pequeña</v>
+      </c>
+      <c r="N115" s="13" t="str">
+        <v>290 × 100</v>
+      </c>
+      <c r="O115" s="13" t="str">
+        <v>289,1 × 99,1</v>
+      </c>
+      <c r="P115" s="13" t="str">
+        <v>Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B116" s="13" t="str">
+        <v>S05</v>
+      </c>
+      <c r="C116" s="13" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D116" s="13" t="str">
+        <v>Entrepaño columna abierta derecha</v>
+      </c>
+      <c r="E116" s="13" t="str">
+        <v>RH15 Cartagena</v>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="H116" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I116" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="J116" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="K116" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="L116" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="M116" s="13" t="str">
+        <v>Pequeña</v>
+      </c>
+      <c r="N116" s="13" t="str">
+        <v>115 × 100</v>
+      </c>
+      <c r="O116" s="13" t="str">
+        <v>114,1 × 99,1</v>
+      </c>
+      <c r="P116" s="13" t="str">
+        <v>Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B117" s="13" t="str">
+        <v>S06</v>
+      </c>
+      <c r="C117" s="13" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D117" s="13" t="str">
+        <v>Tapa RH15 portadora del espejo</v>
+      </c>
+      <c r="E117" s="13" t="str">
+        <v>RH15 Cartagena</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H117" s="13" t="n">
+        <v>320</v>
+      </c>
+      <c r="I117" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="J117" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="K117" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="L117" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="M117" s="13" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="N117" s="13" t="str">
+        <v>500 × 320</v>
+      </c>
+      <c r="O117" s="13" t="str">
+        <v>499,1 × 319,1</v>
+      </c>
+      <c r="P117" s="13" t="str">
+        <v>Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B118" s="13" t="str">
+        <v>F01</v>
+      </c>
+      <c r="C118" s="13" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D118" s="13" t="str">
+        <v>Fondo blanco de 6 mm</v>
+      </c>
+      <c r="E118" s="13" t="str">
+        <v>Fondo melamina blanco RH6</v>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="13" t="n">
+        <v>496</v>
+      </c>
+      <c r="H118" s="13" t="n">
+        <v>446</v>
+      </c>
+      <c r="I118" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="J118" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="K118" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="L118" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="M118" s="13" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="N118" s="13" t="str">
         <v>496 × 446</v>
       </c>
-      <c r="O114" s="16" t="str">
+      <c r="O118" s="13" t="str">
         <v>495,1 × 445,1</v>
       </c>
-      <c r="P114" s="17" t="str">
+      <c r="P118" s="13" t="str">
         <v>Fondo aplicado por detrás, retranqueado 2 mm de los bordes. Reutilización de sobrantes de cocina solo se comprobará en la optimización conjunta final. No soporta el anclaje del gabinete. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:P114"/>
+  <autoFilter ref="A6:P118"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6029,7 +6229,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Cortes pasantes, sin rotar por la veta, refilado 10 mm por lado y sierra 4 mm. El plano de corte definitivo lo define la seccionadora del proveedor.</x:v>
+        <x:v>Cortes pasantes, sin rotar por la veta, refilado 10 mm por lado y sierra 5 mm. El plano de corte definitivo lo define la seccionadora del proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6054,10 +6254,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="18" t="n">
-        <x:v>0.969</x:v>
+        <x:v>0.954</x:v>
       </x:c>
       <x:c r="D7" s="17" t="str">
-        <x:v>Clóset C3-011, Clóset C3-023, Cocina P016, Cocina P011, Cocina P002, Cocina P019, Cocina P019, Cocina P018, Cocina P003, Cocina P003</x:v>
+        <x:v>Clóset C3-023, Clóset C3-023, Clóset C3-024, Cocina P016, Cocina P011, Cocina P040, Cocina P043, Clóset C3-019, Clóset C3-019, Baño B04, Baño B04, Cocina P003, Cocina P003</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28.799999237060547">
@@ -6068,10 +6268,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>0.886</x:v>
+        <x:v>0.928</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>Clóset C3-023, Clóset C3-009, Clóset C3-010, Clóset C3-012, Clóset C3-006, Clóset C3-020, Cocina P040, Cocina P041, Cocina P043, Clóset C3-019, Baño B04, Baño S05</x:v>
+        <x:v>Clóset C3-001, Clóset C3-001, Clóset C3-002, Clóset C3-010, Clóset C3-012, Cocina P041, Baño S05</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6082,10 +6282,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:v>0.89</x:v>
+        <x:v>0.924</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
-        <x:v>Clóset C3-005, Cocina P037, Clóset C3-003, Cocina P001, Cocina P001, Cocina P024, Baño B02, Clóset C3-021, Baño S03, Baño B04</x:v>
+        <x:v>Clóset C3-009, Cocina P037, Clóset C3-003, Cocina P001, Cocina P001, Cocina P006, Cocina P024, Cocina P013, Cocina P070, Cocina P063, Cocina P064, Baño B02, Baño S01</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6096,10 +6296,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>0.895</x:v>
+        <x:v>0.934</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>Clóset C3-001, Clóset C3-001, Cocina P006, Cocina P006, Cocina P013, Cocina P070, Cocina P063, Cocina P064</x:v>
+        <x:v>Cocina P006, Cocina P012, Cocina P012, Cocina P023, Cocina P023, Cocina P030, Cocina P030, Clóset C3-004, Clóset C3-017, Cocina P022, Cocina P027, Cocina P028</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6110,10 +6310,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:v>0.885</x:v>
+        <x:v>0.883</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>Clóset C3-002, Cocina P012, Cocina P012, Cocina P023, Cocina P023, Clóset C3-017, Clóset C3-017, Cocina P022, Cocina P029, Baño B01</x:v>
+        <x:v>Clóset C3-006, Clóset C3-017, Clóset C3-017, Cocina P029, Cocina P017, Cocina P007, Cocina P009, Cocina P056, Cocina P057, Cocina P039, Cocina P039, Cocina P050, Cocina P050, Cocina P058, Cocina P031, Cocina P002, Cocina P025, Cocina P008, Cocina P061, Cocina P010, Cocina P018</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="43.20000076293945">
@@ -6124,10 +6324,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="18" t="n">
-        <x:v>0.909</x:v>
+        <x:v>0.784</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>Cocina P030, Cocina P030, Clóset C3-004, Clóset C3-017, Cocina P017, Cocina P009, Cocina P027, Cocina P028, Clóset C3-024, Cocina P056, Cocina P057, Cocina P039, Cocina P039, Cocina P038, Cocina P066, Clóset C3-014, Clóset C3-013, Clóset C3-007, Baño S02, Cocina P060, Baño B05, Clóset C3-019, Clóset C3-019, Baño S04, Baño S04</x:v>
+        <x:v>Cocina P058, Cocina P065, Cocina P065, Cocina P059, Cocina P054, Baño B01, Baño B01, Cocina P049, Cocina P034, Cocina P051, Cocina P052, Baño B03, Cocina P046, Cocina P047, Cocina P020, Cocina P035, Baño B06, Cocina P036, Cocina P055, Cocina P055, Clóset C3-016, Clóset C3-016, Clóset C3-016, Baño S01, Baño S03, Baño S04, Baño S04</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="43.20000076293945">
@@ -6138,10 +6338,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="18" t="n">
-        <x:v>0.897</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>Cocina P007, Cocina P050, Cocina P050, Cocina P058, Cocina P058, Cocina P065, Cocina P065, Cocina P059, Cocina P031, Cocina P054, Baño B01, Cocina P051, Cocina P052, Clóset C3-015, Clóset C3-015, Clóset C3-015, Cocina P044, Cocina P005, Cocina P038, Cocina P067, Cocina P045, Cocina P055, Cocina P055, Clóset C3-008, Cocina P025, Cocina P025, Cocina P014, Cocina P014, Cocina P061</x:v>
+        <x:v>Clóset C3-027, Clóset C3-028, Clóset C3-020, Cocina P021, Clóset C3-015, Clóset C3-015, Clóset C3-015, Baño S06, Cocina P044, Cocina P005, Cocina P038, Cocina P038, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Cocina P066, Cocina P067, Cocina P045, Cocina P045, Cocina P069, Clóset C3-016, Clóset C3-016, Clóset C3-016, Cocina P025, Cocina P014, Cocina P014, Baño S02, Baño S02, Cocina P019, Cocina P019, Cocina P032, Cocina P032</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="57.599998474121094">
@@ -6152,10 +6352,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="18" t="n">
-        <x:v>0.731</x:v>
+        <x:v>0.228</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Cocina P049, Cocina P034, Baño B03, Cocina P046, Cocina P047, Cocina P020, Cocina P021, Baño S06, Cocina P035, Baño B06, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Cocina P036, Cocina P045, Cocina P069, Clóset C3-016, Clóset C3-016, Clóset C3-016, Clóset C3-016, Clóset C3-016, Clóset C3-016, Cocina P008, Baño S01, Baño S01, Cocina P010, Baño S02, Cocina P018, Clóset C3-022, Clóset C3-022, Clóset C3-022, Cocina P032, Cocina P032, Cocina P071</x:v>
+        <x:v>Clóset C3-021, Clóset C3-026, Clóset C3-014, Clóset C3-030, Clóset C3-013, Clóset C3-025, Clóset C3-008, Clóset C3-029, Clóset C3-007, Cocina P018, Cocina P060, Baño B05, Clóset C3-022, Clóset C3-022, Clóset C3-022, Cocina P071, Clóset C3-019</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6289,10 +6489,10 @@
         <x:v>Clóset</x:v>
       </x:c>
       <x:c r="C13" s="13" t="n">
-        <x:v>51.885</x:v>
+        <x:v>59.795</x:v>
       </x:c>
       <x:c r="D13" s="13" t="n">
-        <x:v>80</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6314,13 +6514,13 @@
         <x:v>Flexible 0,45 mm</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Total · comprar 172 m</x:v>
+        <x:v>Total · comprar 181 m</x:v>
       </x:c>
       <x:c r="C15" s="14" t="n">
-        <x:v>141.296</x:v>
+        <x:v>149.206</x:v>
       </x:c>
       <x:c r="D15" s="14" t="n">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6402,7 +6602,7 @@
         <x:v>2926976</x:v>
       </x:c>
       <x:c r="H10" s="17" t="str">
-        <x:v>Encaje conjunto de las piezas RH15 de los tres muebles en 8 láminas (hoja Láminas). Por separado serían 10.</x:v>
+        <x:v>Encaje conjunto de las piezas RH15 de los tres muebles en 8 láminas (hoja Láminas). Por separado serían 9.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6510,7 +6710,7 @@
         <x:v>285600</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>Necesario 172 m: 141,3 m netos + 5 cm por borde (300 bordes) + 10 %. Sobran unos 28 m para cantear en el armado las piezas pequeñas que no acepte la máquina.</x:v>
+        <x:v>Necesario 181 m: 149,2 m netos + 5 cm por borde (306 bordes) + 10 %. Sobran unos 19 m para cantear en el armado las piezas pequeñas que no acepte la máquina.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28.799999237060547">
@@ -7090,7 +7290,7 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
-        <x:v>Incluye fijación de fondos, estructura y refuerzos de RH; el bastidor del riel se lista aparte. El extremo derecho queda libre: no puede anclarse al muro lateral derecho. Definir anclaje posterior y lateral izquierdo según muro.</x:v>
+        <x:v>Unir el marco completo C3-025 a C3-030 a laterales, divisor, pisos y tapas. Dimensionar anclajes al muro posterior resistente y al izquierdo. No fijar solo al estuco. El lateral derecho queda libre: el montante se une a la caja y al muro de fondo, no a una pared lateral inexistente. El marco abierto no se da por equivalente a un panel arriostrante.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72">
@@ -7859,7 +8059,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -7915,7 +8115,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7943,7 +8143,7 @@
         <x:v>Travesaño de canto</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -7985,7 +8185,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8027,7 +8227,7 @@
         <x:v>PROVISIONAL larguero bajo plataforma basurero</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 549.1 × 59.1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
+        <x:v>Si no la cantean: cortar a 549,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="28.799999237060547">
@@ -8041,7 +8241,7 @@
         <x:v>PROVISIONAL travesaño bajo plataforma basurero</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 312.1 × 59.1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
+        <x:v>Si no la cantean: cortar a 312,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">

--- a/compras-proyecto.xlsx
+++ b/compras-proyecto.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="R22261d597eb64c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="2" r:id="R1aee4edc6ec641ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Láminas" sheetId="3" r:id="R5cdc49ae4d094ad2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="4" r:id="R9f55a881f64e4ed8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="5" r:id="R89e54929ecef4b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloqueos" sheetId="6" r:id="Rd41c2da8a27c4626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En el armado" sheetId="7" r:id="R87b8fa41abe74842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="Rd982a223076d41a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="2" r:id="R0946d8444f2a48c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Láminas" sheetId="3" r:id="R51bf6acb0bac44a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="4" r:id="R9c698a3281754c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="5" r:id="R0f22885d2eb641e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloqueos" sheetId="6" r:id="R16fc8b08e6a54048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En el armado" sheetId="7" r:id="Raaf837382d3f40f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +24,7 @@
     <x:numFmt numFmtId="200" formatCode="General"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -35,23 +35,23 @@
     <x:font>
       <x:b/>
       <x:sz val="14"/>
-      <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:i/>
-      <x:sz val="11"/>
-      <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -79,23 +79,23 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -112,10 +112,88 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
 </x:styleSheet>
 </file>
 
@@ -391,21 +469,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="42" customWidth="1"/>
-    <x:col min="2" max="3" width="16" customWidth="1"/>
+    <x:col min="2" max="2" width="16" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
     <x:col min="4" max="4" width="90" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Compras del proyecto · cocina, clóset y baño</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Estimación conjunta del 28/10/2026, generada desde los Excel de cada mueble (herramientas/build_compras_proyecto.py).</x:v>
+        <x:v>Estimación conjunta del 29/10/2026, generada desde los Excel de cada mueble (herramientas/build_compras_proyecto.py).</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -475,7 +554,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="13" t="str">
-        <x:v>Sobran unos 19 m para cantear piezas pequeñas en el armado.</x:v>
+        <x:v>Sobran unos 14 m para cantear piezas pequeñas en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -525,7 +604,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -533,15 +612,19 @@
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="12" width="7" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="7" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18">
+    <row r="2">
       <c r="A2" s="10" t="str">
         <v>Pedido de corte y canteado · pedido único de los tres muebles</v>
       </c>
@@ -556,7 +639,7 @@
         <v>Supuestos de cada despiece: el proveedor pide medida terminada y descuenta el canto; piezas pequeñas = lado menor &lt; 100 mm o mayor &lt; 250 mm. Si la sucursal pide medida de corte, usar la columna «Corte sin canto».</v>
       </c>
     </row>
-    <row r="6" ht="28.799999237060547">
+    <row r="6">
       <c r="A6" s="12" t="str">
         <v>Mueble</v>
       </c>
@@ -606,7 +689,7 @@
         <v>Observaciones</v>
       </c>
     </row>
-    <row r="7" ht="28.799999237060547">
+    <row r="7">
       <c r="A7" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -706,7 +789,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="9" ht="43.20000076293945">
+    <row r="9">
       <c r="A9" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -753,7 +836,7 @@
         <v>150 × 99,1</v>
       </c>
       <c r="P9" s="17" t="str">
-        <v>Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="10">
@@ -906,7 +989,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="13" ht="28.799999237060547">
+    <row r="13">
       <c r="A13" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1003,10 +1086,10 @@
         <v>570 × 99,55</v>
       </c>
       <c r="P14" s="17" t="str">
-        <v>Si no la cantean: cortar a 570 × 99,55 y cantear en el armado.</v>
-      </c>
-    </row>
-    <row r="15" ht="28.799999237060547">
+        <v>Si no la cantean: cortar a 570 × 99.55 y cantear en el armado.</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1056,7 +1139,7 @@
         <v>Su altura se fija en el armado según el manual del horno; si pide más ventilación atrás, recortar el borde trasero (sin canto).</v>
       </c>
     </row>
-    <row r="16" ht="28.799999237060547">
+    <row r="16">
       <c r="A16" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1103,10 +1186,10 @@
         <v>570 × 79,55</v>
       </c>
       <c r="P16" s="17" t="str">
-        <v>Si no la cantean: cortar a 570 × 79,55 y cantear en el armado.</v>
-      </c>
-    </row>
-    <row r="17" ht="43.20000076293945">
+        <v>Si no la cantean: cortar a 570 × 79.55 y cantear en el armado.</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1156,7 +1239,7 @@
         <v>Pedida 15 mm más alta (160 en vez de 145): en el armado, recortar el borde superior —oculto bajo el mesón y sin canto— según el horno instalado.</v>
       </c>
     </row>
-    <row r="18" ht="28.799999237060547">
+    <row r="18">
       <c r="A18" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1256,7 +1339,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="20" ht="43.20000076293945">
+    <row r="20">
       <c r="A20" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1303,7 +1386,7 @@
         <v>640 × 99,1</v>
       </c>
       <c r="P20" s="17" t="str">
-        <v>Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="21">
@@ -1503,7 +1586,7 @@
         <v>549,55 × 74,55</v>
       </c>
       <c r="P24" s="17" t="str">
-        <v>Si no la cantean: cortar a 549,55 × 74,55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 549.55 × 74.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="25">
@@ -1553,7 +1636,7 @@
         <v>583 × 74,55</v>
       </c>
       <c r="P25" s="17" t="str">
-        <v>Si no la cantean: cortar a 583 × 74,55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 583 × 74.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="26">
@@ -1706,7 +1789,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="29" ht="28.799999237060547">
+    <row r="29">
       <c r="A29" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1806,7 +1889,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="31" ht="43.20000076293945">
+    <row r="31">
       <c r="A31" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -1853,7 +1936,7 @@
         <v>669,1 × 99,1</v>
       </c>
       <c r="P31" s="17" t="str">
-        <v>Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="32">
@@ -2006,7 +2089,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="35" ht="28.799999237060547">
+    <row r="35">
       <c r="A35" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2056,7 +2139,7 @@
         <v>P029: flexible 0,45 mm en los cuatro bordes. Recorte de sifón y tuberías en obra: sellar el corte.</v>
       </c>
     </row>
-    <row r="36" ht="28.799999237060547">
+    <row r="36">
       <c r="A36" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2156,7 +2239,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="38" ht="43.20000076293945">
+    <row r="38">
       <c r="A38" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2203,7 +2286,7 @@
         <v>370 × 99,1</v>
       </c>
       <c r="P38" s="17" t="str">
-        <v>Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
+        <v>Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</v>
       </c>
     </row>
     <row r="39">
@@ -2256,7 +2339,7 @@
         <v>—</v>
       </c>
     </row>
-    <row r="40" ht="28.799999237060547">
+    <row r="40">
       <c r="A40" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2503,7 +2586,7 @@
         <v>1274,1 × 96,1</v>
       </c>
       <c r="P44" s="17" t="str">
-        <v>Si no la cantean: cortar a 1274,1 × 96,1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 1274.1 × 96.1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="45">
@@ -2826,7 +2909,7 @@
         <v>2</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>320</v>
@@ -2847,16 +2930,16 @@
         <v>Normal</v>
       </c>
       <c r="N51" s="16" t="str">
-        <v>350 × 320</v>
+        <v>450 × 320</v>
       </c>
       <c r="O51" s="16" t="str">
-        <v>349,1 × 319,55</v>
+        <v>449,1 × 319,55</v>
       </c>
       <c r="P51" s="17" t="str">
         <v>—</v>
       </c>
     </row>
-    <row r="52" ht="28.799999237060547">
+    <row r="52">
       <c r="A52" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2867,7 +2950,7 @@
         <v>S2 Gabinete ducto 60</v>
       </c>
       <c r="D52" s="17" t="str">
-        <v>Techo (perforar solo si el ducto sale hacia arriba; definir con manual)</v>
+        <v>Techo de S2; sin perforación de ducto prevista</v>
       </c>
       <c r="E52" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -2903,10 +2986,10 @@
         <v>570 × 319,55</v>
       </c>
       <c r="P52" s="17" t="str">
-        <v>Perforación del ducto en obra, según manual de la campana.</v>
-      </c>
-    </row>
-    <row r="53" ht="43.20000076293945">
+        <v>Montaje de campana en recirculación: NO perforar para un ducto supuesto. Soporte bajo piso elevado y encuentro con P071 pendientes de definir antes del armado.</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="16" t="str">
         <v>Cocina</v>
       </c>
@@ -2917,7 +3000,7 @@
         <v>S2 Gabinete ducto 60</v>
       </c>
       <c r="D53" s="17" t="str">
-        <v>Piso elevado 40 mm para agarre inferior; perforar para ducto (diámetro y posición según manual de campana)</v>
+        <v>Piso elevado de S2; soporte de campana por definir</v>
       </c>
       <c r="E53" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -2953,7 +3036,7 @@
         <v>570 × 319,55</v>
       </c>
       <c r="P53" s="17" t="str">
-        <v>Perforación del ducto en obra, según manual de la campana.</v>
+        <v>Montaje de campana en recirculación: NO perforar para un ducto supuesto. Soporte bajo piso elevado y encuentro con P071 pendientes de definir antes del armado.</v>
       </c>
     </row>
     <row r="54">
@@ -2979,7 +3062,7 @@
         <v>596</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>346</v>
+        <v>446</v>
       </c>
       <c r="I54" s="16" t="str">
         <v>—</v>
@@ -2997,10 +3080,10 @@
         <v>Sin canto</v>
       </c>
       <c r="N54" s="16" t="str">
-        <v>596 × 346</v>
+        <v>596 × 446</v>
       </c>
       <c r="O54" s="16" t="str">
-        <v>596 × 346</v>
+        <v>596 × 446</v>
       </c>
       <c r="P54" s="17" t="str">
         <v>—</v>
@@ -3026,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>347</v>
+        <v>447</v>
       </c>
       <c r="H55" s="16" t="n">
         <v>597</v>
@@ -3047,45 +3130,45 @@
         <v>Normal</v>
       </c>
       <c r="N55" s="16" t="str">
-        <v>347 × 597</v>
+        <v>447 × 597</v>
       </c>
       <c r="O55" s="16" t="str">
-        <v>343 × 593</v>
+        <v>443 × 593</v>
       </c>
       <c r="P55" s="17" t="str">
         <v>—</v>
       </c>
     </row>
-    <row r="56" ht="43.20000076293945">
+    <row r="56">
       <c r="A56" s="16" t="str">
         <v>Cocina</v>
       </c>
       <c r="B56" s="16" t="str">
-        <v>P071</v>
+        <v>P050</v>
       </c>
       <c r="C56" s="16" t="str">
-        <v>S2 Gabinete ducto 60</v>
+        <v>S3 Alacena 65,5</v>
       </c>
       <c r="D56" s="17" t="str">
-        <v>Faja retranqueada de agarre sobre campana</v>
+        <v>Lateral</v>
       </c>
       <c r="E56" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="16" t="n">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="I56" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J56" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K56" s="16" t="str">
         <v>F</v>
@@ -3094,16 +3177,16 @@
         <v>F</v>
       </c>
       <c r="M56" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N56" s="16" t="str">
-        <v>570 × 60</v>
+        <v>700 × 320</v>
       </c>
       <c r="O56" s="16" t="str">
-        <v>569,1 × 59,1</v>
+        <v>699,1 × 319,55</v>
       </c>
       <c r="P56" s="17" t="str">
-        <v>Si no la cantean: cortar a 569,1 × 59,1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="57">
@@ -3111,22 +3194,22 @@
         <v>Cocina</v>
       </c>
       <c r="B57" s="16" t="str">
-        <v>P050</v>
+        <v>P051</v>
       </c>
       <c r="C57" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D57" s="17" t="str">
-        <v>Lateral</v>
+        <v>Techo</v>
       </c>
       <c r="E57" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>700</v>
+        <v>625</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>320</v>
@@ -3138,19 +3221,19 @@
         <v>—</v>
       </c>
       <c r="K57" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L57" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M57" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N57" s="16" t="str">
-        <v>700 × 320</v>
+        <v>625 × 320</v>
       </c>
       <c r="O57" s="16" t="str">
-        <v>699,1 × 319,55</v>
+        <v>625 × 319,55</v>
       </c>
       <c r="P57" s="17" t="str">
         <v>—</v>
@@ -3161,13 +3244,13 @@
         <v>Cocina</v>
       </c>
       <c r="B58" s="16" t="str">
-        <v>P051</v>
+        <v>P052</v>
       </c>
       <c r="C58" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D58" s="17" t="str">
-        <v>Techo</v>
+        <v>Piso</v>
       </c>
       <c r="E58" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3211,28 +3294,28 @@
         <v>Cocina</v>
       </c>
       <c r="B59" s="16" t="str">
-        <v>P052</v>
+        <v>P053</v>
       </c>
       <c r="C59" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D59" s="17" t="str">
-        <v>Piso</v>
+        <v>Fondo</v>
       </c>
       <c r="E59" s="16" t="str">
-        <v>Melamina Cartagena RH 15</v>
+        <v>Fondo melamina 6</v>
       </c>
       <c r="F59" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="16" t="n">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>320</v>
+        <v>696</v>
       </c>
       <c r="I59" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="J59" s="16" t="str">
         <v>—</v>
@@ -3244,13 +3327,13 @@
         <v>—</v>
       </c>
       <c r="M59" s="16" t="str">
-        <v>Normal</v>
+        <v>Sin canto</v>
       </c>
       <c r="N59" s="16" t="str">
-        <v>625 × 320</v>
+        <v>651 × 696</v>
       </c>
       <c r="O59" s="16" t="str">
-        <v>625 × 319,55</v>
+        <v>651 × 696</v>
       </c>
       <c r="P59" s="17" t="str">
         <v>—</v>
@@ -3261,28 +3344,28 @@
         <v>Cocina</v>
       </c>
       <c r="B60" s="16" t="str">
-        <v>P053</v>
+        <v>P054</v>
       </c>
       <c r="C60" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D60" s="17" t="str">
-        <v>Fondo</v>
+        <v>División vertical</v>
       </c>
       <c r="E60" s="16" t="str">
-        <v>Fondo melamina 6</v>
+        <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F60" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>696</v>
+        <v>320</v>
       </c>
       <c r="I60" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="J60" s="16" t="str">
         <v>—</v>
@@ -3294,13 +3377,13 @@
         <v>—</v>
       </c>
       <c r="M60" s="16" t="str">
-        <v>Sin canto</v>
+        <v>Normal</v>
       </c>
       <c r="N60" s="16" t="str">
-        <v>651 × 696</v>
+        <v>670 × 320</v>
       </c>
       <c r="O60" s="16" t="str">
-        <v>651 × 696</v>
+        <v>670 × 319,55</v>
       </c>
       <c r="P60" s="17" t="str">
         <v>—</v>
@@ -3311,25 +3394,25 @@
         <v>Cocina</v>
       </c>
       <c r="B61" s="16" t="str">
-        <v>P054</v>
+        <v>P055</v>
       </c>
       <c r="C61" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D61" s="17" t="str">
-        <v>División vertical</v>
+        <v>Entrepaño regulable</v>
       </c>
       <c r="E61" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="16" t="n">
-        <v>670</v>
+        <v>303</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="I61" s="16" t="str">
         <v>F</v>
@@ -3347,10 +3430,10 @@
         <v>Normal</v>
       </c>
       <c r="N61" s="16" t="str">
-        <v>670 × 320</v>
+        <v>303 × 300</v>
       </c>
       <c r="O61" s="16" t="str">
-        <v>670 × 319,55</v>
+        <v>303 × 299,55</v>
       </c>
       <c r="P61" s="17" t="str">
         <v>—</v>
@@ -3361,46 +3444,46 @@
         <v>Cocina</v>
       </c>
       <c r="B62" s="16" t="str">
-        <v>P055</v>
+        <v>P056</v>
       </c>
       <c r="C62" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D62" s="17" t="str">
-        <v>Entrepaño regulable</v>
+        <v>Puerta izquierda</v>
       </c>
       <c r="E62" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F62" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>303</v>
+        <v>717</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>300</v>
+        <v>324.5</v>
       </c>
       <c r="I62" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J62" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="K62" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="L62" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="M62" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N62" s="16" t="str">
-        <v>303 × 300</v>
+        <v>717 × 324.5</v>
       </c>
       <c r="O62" s="16" t="str">
-        <v>303 × 299,55</v>
+        <v>713 × 320,5</v>
       </c>
       <c r="P62" s="17" t="str">
         <v>—</v>
@@ -3411,13 +3494,13 @@
         <v>Cocina</v>
       </c>
       <c r="B63" s="16" t="str">
-        <v>P056</v>
+        <v>P057</v>
       </c>
       <c r="C63" s="16" t="str">
         <v>S3 Alacena 65,5</v>
       </c>
       <c r="D63" s="17" t="str">
-        <v>Puerta izquierda</v>
+        <v>Puerta derecha</v>
       </c>
       <c r="E63" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3447,7 +3530,7 @@
         <v>Normal</v>
       </c>
       <c r="N63" s="16" t="str">
-        <v>717 × 324,5</v>
+        <v>717 × 324.5</v>
       </c>
       <c r="O63" s="16" t="str">
         <v>713 × 320,5</v>
@@ -3461,46 +3544,46 @@
         <v>Cocina</v>
       </c>
       <c r="B64" s="16" t="str">
-        <v>P057</v>
+        <v>P058</v>
       </c>
       <c r="C64" s="16" t="str">
-        <v>S3 Alacena 65,5</v>
+        <v>S4 Platero 71,5</v>
       </c>
       <c r="D64" s="17" t="str">
-        <v>Puerta derecha</v>
+        <v>Lateral</v>
       </c>
       <c r="E64" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F64" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="16" t="n">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>324.5</v>
+        <v>320</v>
       </c>
       <c r="I64" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J64" s="16" t="str">
-        <v>R</v>
+        <v>—</v>
       </c>
       <c r="K64" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L64" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M64" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N64" s="16" t="str">
-        <v>717 × 324,5</v>
+        <v>700 × 320</v>
       </c>
       <c r="O64" s="16" t="str">
-        <v>713 × 320,5</v>
+        <v>699,1 × 319,55</v>
       </c>
       <c r="P64" s="17" t="str">
         <v>—</v>
@@ -3511,22 +3594,22 @@
         <v>Cocina</v>
       </c>
       <c r="B65" s="16" t="str">
-        <v>P058</v>
+        <v>P059</v>
       </c>
       <c r="C65" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D65" s="17" t="str">
-        <v>Lateral</v>
+        <v>Techo</v>
       </c>
       <c r="E65" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="H65" s="16" t="n">
         <v>320</v>
@@ -3538,19 +3621,19 @@
         <v>—</v>
       </c>
       <c r="K65" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L65" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M65" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N65" s="16" t="str">
-        <v>700 × 320</v>
+        <v>685 × 320</v>
       </c>
       <c r="O65" s="16" t="str">
-        <v>699,1 × 319,55</v>
+        <v>685 × 319,55</v>
       </c>
       <c r="P65" s="17" t="str">
         <v>—</v>
@@ -3561,13 +3644,13 @@
         <v>Cocina</v>
       </c>
       <c r="B66" s="16" t="str">
-        <v>P059</v>
+        <v>P060</v>
       </c>
       <c r="C66" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D66" s="17" t="str">
-        <v>Techo</v>
+        <v>Listón inferior delantero</v>
       </c>
       <c r="E66" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3579,31 +3662,31 @@
         <v>685</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="I66" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J66" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="K66" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="L66" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="M66" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N66" s="16" t="str">
-        <v>685 × 320</v>
+        <v>685 × 60</v>
       </c>
       <c r="O66" s="16" t="str">
-        <v>685 × 319,55</v>
+        <v>684,1 × 59,1</v>
       </c>
       <c r="P66" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 684.1 × 59.1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="67">
@@ -3611,13 +3694,13 @@
         <v>Cocina</v>
       </c>
       <c r="B67" s="16" t="str">
-        <v>P060</v>
+        <v>P061</v>
       </c>
       <c r="C67" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D67" s="17" t="str">
-        <v>Listón inferior delantero</v>
+        <v>Listón inferior trasero</v>
       </c>
       <c r="E67" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3629,7 +3712,7 @@
         <v>685</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I67" s="16" t="str">
         <v>F</v>
@@ -3647,13 +3730,13 @@
         <v>Pequeña</v>
       </c>
       <c r="N67" s="16" t="str">
-        <v>685 × 60</v>
+        <v>685 × 80</v>
       </c>
       <c r="O67" s="16" t="str">
-        <v>684,1 × 59,1</v>
+        <v>684,1 × 79,1</v>
       </c>
       <c r="P67" s="17" t="str">
-        <v>Si no la cantean: cortar a 684,1 × 59,1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 684.1 × 79.1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="68">
@@ -3661,49 +3744,49 @@
         <v>Cocina</v>
       </c>
       <c r="B68" s="16" t="str">
-        <v>P061</v>
+        <v>P062</v>
       </c>
       <c r="C68" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D68" s="17" t="str">
-        <v>Listón inferior trasero</v>
+        <v>Fondo</v>
       </c>
       <c r="E68" s="16" t="str">
-        <v>Melamina Cartagena RH 15</v>
+        <v>Fondo melamina 6</v>
       </c>
       <c r="F68" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>685</v>
+        <v>711</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>80</v>
+        <v>696</v>
       </c>
       <c r="I68" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="J68" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K68" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L68" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M68" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Sin canto</v>
       </c>
       <c r="N68" s="16" t="str">
-        <v>685 × 80</v>
+        <v>711 × 696</v>
       </c>
       <c r="O68" s="16" t="str">
-        <v>684,1 × 79,1</v>
+        <v>711 × 696</v>
       </c>
       <c r="P68" s="17" t="str">
-        <v>Si no la cantean: cortar a 684,1 × 79,1 y cantear en el armado.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="69">
@@ -3711,46 +3794,46 @@
         <v>Cocina</v>
       </c>
       <c r="B69" s="16" t="str">
-        <v>P062</v>
+        <v>P063</v>
       </c>
       <c r="C69" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D69" s="17" t="str">
-        <v>Fondo</v>
+        <v>Puerta izquierda</v>
       </c>
       <c r="E69" s="16" t="str">
-        <v>Fondo melamina 6</v>
+        <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F69" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>696</v>
+        <v>354.5</v>
       </c>
       <c r="I69" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="J69" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="K69" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="L69" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="M69" s="16" t="str">
-        <v>Sin canto</v>
+        <v>Normal</v>
       </c>
       <c r="N69" s="16" t="str">
-        <v>711 × 696</v>
+        <v>717 × 354.5</v>
       </c>
       <c r="O69" s="16" t="str">
-        <v>711 × 696</v>
+        <v>713 × 350,5</v>
       </c>
       <c r="P69" s="17" t="str">
         <v>—</v>
@@ -3761,13 +3844,13 @@
         <v>Cocina</v>
       </c>
       <c r="B70" s="16" t="str">
-        <v>P063</v>
+        <v>P064</v>
       </c>
       <c r="C70" s="16" t="str">
         <v>S4 Platero 71,5</v>
       </c>
       <c r="D70" s="17" t="str">
-        <v>Puerta izquierda</v>
+        <v>Puerta derecha</v>
       </c>
       <c r="E70" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3797,7 +3880,7 @@
         <v>Normal</v>
       </c>
       <c r="N70" s="16" t="str">
-        <v>717 × 354,5</v>
+        <v>717 × 354.5</v>
       </c>
       <c r="O70" s="16" t="str">
         <v>713 × 350,5</v>
@@ -3811,46 +3894,46 @@
         <v>Cocina</v>
       </c>
       <c r="B71" s="16" t="str">
-        <v>P064</v>
+        <v>P065</v>
       </c>
       <c r="C71" s="16" t="str">
-        <v>S4 Platero 71,5</v>
+        <v>S5 Alacena 40</v>
       </c>
       <c r="D71" s="17" t="str">
-        <v>Puerta derecha</v>
+        <v>Lateral</v>
       </c>
       <c r="E71" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="16" t="n">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>354.5</v>
+        <v>320</v>
       </c>
       <c r="I71" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J71" s="16" t="str">
-        <v>R</v>
+        <v>—</v>
       </c>
       <c r="K71" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L71" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M71" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N71" s="16" t="str">
-        <v>717 × 354,5</v>
+        <v>700 × 320</v>
       </c>
       <c r="O71" s="16" t="str">
-        <v>713 × 350,5</v>
+        <v>699,1 × 319,55</v>
       </c>
       <c r="P71" s="17" t="str">
         <v>—</v>
@@ -3861,22 +3944,22 @@
         <v>Cocina</v>
       </c>
       <c r="B72" s="16" t="str">
-        <v>P065</v>
+        <v>P066</v>
       </c>
       <c r="C72" s="16" t="str">
         <v>S5 Alacena 40</v>
       </c>
       <c r="D72" s="17" t="str">
-        <v>Lateral</v>
+        <v>Techo</v>
       </c>
       <c r="E72" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="H72" s="16" t="n">
         <v>320</v>
@@ -3888,19 +3971,19 @@
         <v>—</v>
       </c>
       <c r="K72" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L72" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M72" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N72" s="16" t="str">
-        <v>700 × 320</v>
+        <v>370 × 320</v>
       </c>
       <c r="O72" s="16" t="str">
-        <v>699,1 × 319,55</v>
+        <v>370 × 319,55</v>
       </c>
       <c r="P72" s="17" t="str">
         <v>—</v>
@@ -3911,13 +3994,13 @@
         <v>Cocina</v>
       </c>
       <c r="B73" s="16" t="str">
-        <v>P066</v>
+        <v>P067</v>
       </c>
       <c r="C73" s="16" t="str">
         <v>S5 Alacena 40</v>
       </c>
       <c r="D73" s="17" t="str">
-        <v>Techo</v>
+        <v>Piso</v>
       </c>
       <c r="E73" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -3961,28 +4044,28 @@
         <v>Cocina</v>
       </c>
       <c r="B74" s="16" t="str">
-        <v>P067</v>
+        <v>P068</v>
       </c>
       <c r="C74" s="16" t="str">
         <v>S5 Alacena 40</v>
       </c>
       <c r="D74" s="17" t="str">
-        <v>Piso</v>
+        <v>Fondo</v>
       </c>
       <c r="E74" s="16" t="str">
-        <v>Melamina Cartagena RH 15</v>
+        <v>Fondo melamina 6</v>
       </c>
       <c r="F74" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="16" t="n">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>320</v>
+        <v>696</v>
       </c>
       <c r="I74" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="J74" s="16" t="str">
         <v>—</v>
@@ -3994,13 +4077,13 @@
         <v>—</v>
       </c>
       <c r="M74" s="16" t="str">
-        <v>Normal</v>
+        <v>Sin canto</v>
       </c>
       <c r="N74" s="16" t="str">
-        <v>370 × 320</v>
+        <v>396 × 696</v>
       </c>
       <c r="O74" s="16" t="str">
-        <v>370 × 319,55</v>
+        <v>396 × 696</v>
       </c>
       <c r="P74" s="17" t="str">
         <v>—</v>
@@ -4011,28 +4094,28 @@
         <v>Cocina</v>
       </c>
       <c r="B75" s="16" t="str">
-        <v>P068</v>
+        <v>P069</v>
       </c>
       <c r="C75" s="16" t="str">
         <v>S5 Alacena 40</v>
       </c>
       <c r="D75" s="17" t="str">
-        <v>Fondo</v>
+        <v>Entrepaño regulable</v>
       </c>
       <c r="E75" s="16" t="str">
-        <v>Fondo melamina 6</v>
+        <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F75" s="16" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="16" t="n">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>696</v>
+        <v>300</v>
       </c>
       <c r="I75" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="J75" s="16" t="str">
         <v>—</v>
@@ -4044,13 +4127,13 @@
         <v>—</v>
       </c>
       <c r="M75" s="16" t="str">
-        <v>Sin canto</v>
+        <v>Normal</v>
       </c>
       <c r="N75" s="16" t="str">
-        <v>396 × 696</v>
+        <v>368 × 300</v>
       </c>
       <c r="O75" s="16" t="str">
-        <v>396 × 696</v>
+        <v>368 × 299,55</v>
       </c>
       <c r="P75" s="17" t="str">
         <v>—</v>
@@ -4061,13 +4144,13 @@
         <v>Cocina</v>
       </c>
       <c r="B76" s="16" t="str">
-        <v>P069</v>
+        <v>P070</v>
       </c>
       <c r="C76" s="16" t="str">
         <v>S5 Alacena 40</v>
       </c>
       <c r="D76" s="17" t="str">
-        <v>Entrepaño regulable</v>
+        <v>Puerta</v>
       </c>
       <c r="E76" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -4076,31 +4159,31 @@
         <v>1</v>
       </c>
       <c r="G76" s="16" t="n">
-        <v>368</v>
+        <v>717</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="I76" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J76" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="K76" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="L76" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="M76" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N76" s="16" t="str">
-        <v>368 × 300</v>
+        <v>717 × 397</v>
       </c>
       <c r="O76" s="16" t="str">
-        <v>368 × 299,55</v>
+        <v>713 × 393</v>
       </c>
       <c r="P76" s="17" t="str">
         <v>—</v>
@@ -4111,13 +4194,13 @@
         <v>Cocina</v>
       </c>
       <c r="B77" s="16" t="str">
-        <v>P070</v>
+        <v>P075</v>
       </c>
       <c r="C77" s="16" t="str">
-        <v>S5 Alacena 40</v>
+        <v>S2 Gabinete ducto 60</v>
       </c>
       <c r="D77" s="17" t="str">
-        <v>Puerta</v>
+        <v>Base de montaje de campana; taladrar con plantilla real</v>
       </c>
       <c r="E77" s="16" t="str">
         <v>Melamina Cartagena RH 15</v>
@@ -4126,66 +4209,66 @@
         <v>1</v>
       </c>
       <c r="G77" s="16" t="n">
-        <v>717</v>
+        <v>570</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="I77" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J77" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="K77" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L77" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M77" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N77" s="16" t="str">
-        <v>717 × 397</v>
+        <v>570 × 335</v>
       </c>
       <c r="O77" s="16" t="str">
-        <v>713 × 393</v>
+        <v>569,1 × 334,1</v>
       </c>
       <c r="P77" s="17" t="str">
-        <v>—</v>
+        <v>P075: fijar campana con su plantilla; no taladrar en fábrica. Cuatro escuadras conectan la base a P076. Tornillos sin atravesar el RH15; fijación de campana por fabricante.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="str">
-        <v>Clóset</v>
+        <v>Cocina</v>
       </c>
       <c r="B78" s="16" t="str">
-        <v>C3-001</v>
+        <v>P076</v>
       </c>
       <c r="C78" s="16" t="str">
-        <v>EST</v>
+        <v>S2 Gabinete ducto 60</v>
       </c>
       <c r="D78" s="17" t="str">
-        <v>Lateral exterior</v>
+        <v>Apoyo lateral de base campana; unir a costado y piso</v>
       </c>
       <c r="E78" s="16" t="str">
-        <v>RH15 Cartagena 15 mm</v>
+        <v>Melamina Cartagena RH 15</v>
       </c>
       <c r="F78" s="16" t="n">
         <v>2</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>2280</v>
+        <v>275</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>560</v>
+        <v>70</v>
       </c>
       <c r="I78" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J78" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="K78" s="16" t="str">
         <v>F</v>
@@ -4194,16 +4277,16 @@
         <v>F</v>
       </c>
       <c r="M78" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N78" s="16" t="str">
-        <v>2280 × 560</v>
+        <v>275 × 70</v>
       </c>
       <c r="O78" s="16" t="str">
-        <v>2279,1 × 559,55</v>
+        <v>274,1 × 69,1</v>
       </c>
       <c r="P78" s="17" t="str">
-        <v>Rebaje superior para el listón de pino 4 × 4 en taller.</v>
+        <v>P076: dos apoyos 275 × 70 × 15. Unir a costados y P047. Canto flexible en cuatro bordes; si la máquina rechaza el ancho, terminarlo manualmente. No son rieles de cajón.</v>
       </c>
     </row>
     <row r="79">
@@ -4211,25 +4294,25 @@
         <v>Clóset</v>
       </c>
       <c r="B79" s="16" t="str">
-        <v>C3-002</v>
+        <v>C3-001</v>
       </c>
       <c r="C79" s="16" t="str">
         <v>EST</v>
       </c>
       <c r="D79" s="17" t="str">
-        <v>Divisor central</v>
+        <v>Lateral exterior</v>
       </c>
       <c r="E79" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>2280</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="I79" s="16" t="str">
         <v>F</v>
@@ -4241,19 +4324,19 @@
         <v>F</v>
       </c>
       <c r="L79" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="M79" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N79" s="16" t="str">
-        <v>2280 × 490</v>
+        <v>2280 × 560</v>
       </c>
       <c r="O79" s="16" t="str">
-        <v>2279,55 × 489,55</v>
+        <v>2279,1 × 559,55</v>
       </c>
       <c r="P79" s="17" t="str">
-        <v>—</v>
+        <v>Rebaje superior para el listón de pino 4 × 4 en taller.</v>
       </c>
     </row>
     <row r="80">
@@ -4261,13 +4344,13 @@
         <v>Clóset</v>
       </c>
       <c r="B80" s="16" t="str">
-        <v>C3-003</v>
+        <v>C3-002</v>
       </c>
       <c r="C80" s="16" t="str">
-        <v>B1</v>
+        <v>EST</v>
       </c>
       <c r="D80" s="17" t="str">
-        <v>Piso sobre base</v>
+        <v>Divisor central</v>
       </c>
       <c r="E80" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4276,10 +4359,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="16" t="n">
-        <v>830</v>
+        <v>2280</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>560</v>
+        <v>490</v>
       </c>
       <c r="I80" s="16" t="str">
         <v>F</v>
@@ -4297,10 +4380,10 @@
         <v>Normal</v>
       </c>
       <c r="N80" s="16" t="str">
-        <v>830 × 560</v>
+        <v>2280 × 490</v>
       </c>
       <c r="O80" s="16" t="str">
-        <v>829,55 × 559,55</v>
+        <v>2279,55 × 489,55</v>
       </c>
       <c r="P80" s="17" t="str">
         <v>—</v>
@@ -4311,13 +4394,13 @@
         <v>Clóset</v>
       </c>
       <c r="B81" s="16" t="str">
-        <v>C3-004</v>
+        <v>C3-003</v>
       </c>
       <c r="C81" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D81" s="17" t="str">
-        <v>Tapa superior</v>
+        <v>Piso sobre base</v>
       </c>
       <c r="E81" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4329,7 +4412,7 @@
         <v>830</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>505</v>
+        <v>560</v>
       </c>
       <c r="I81" s="16" t="str">
         <v>F</v>
@@ -4338,7 +4421,7 @@
         <v>—</v>
       </c>
       <c r="K81" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="L81" s="16" t="str">
         <v>—</v>
@@ -4347,10 +4430,10 @@
         <v>Normal</v>
       </c>
       <c r="N81" s="16" t="str">
-        <v>830 × 505</v>
+        <v>830 × 560</v>
       </c>
       <c r="O81" s="16" t="str">
-        <v>830 × 504,55</v>
+        <v>829,55 × 559,55</v>
       </c>
       <c r="P81" s="17" t="str">
         <v>—</v>
@@ -4361,13 +4444,13 @@
         <v>Clóset</v>
       </c>
       <c r="B82" s="16" t="str">
-        <v>C3-025</v>
+        <v>C3-004</v>
       </c>
       <c r="C82" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D82" s="17" t="str">
-        <v>Amarre posterior superior izquierdo</v>
+        <v>Tapa superior</v>
       </c>
       <c r="E82" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4379,7 +4462,7 @@
         <v>830</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>100</v>
+        <v>505</v>
       </c>
       <c r="I82" s="16" t="str">
         <v>F</v>
@@ -4394,16 +4477,16 @@
         <v>—</v>
       </c>
       <c r="M82" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N82" s="16" t="str">
-        <v>830 × 100</v>
+        <v>830 × 505</v>
       </c>
       <c r="O82" s="16" t="str">
-        <v>830 × 99,55</v>
+        <v>830 × 504,55</v>
       </c>
       <c r="P82" s="17" t="str">
-        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="83">
@@ -4411,13 +4494,13 @@
         <v>Clóset</v>
       </c>
       <c r="B83" s="16" t="str">
-        <v>C3-006</v>
+        <v>C3-025</v>
       </c>
       <c r="C83" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D83" s="17" t="str">
-        <v>Piso de maletero</v>
+        <v>Amarre posterior superior izquierdo</v>
       </c>
       <c r="E83" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4429,7 +4512,7 @@
         <v>830</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>475</v>
+        <v>100</v>
       </c>
       <c r="I83" s="16" t="str">
         <v>F</v>
@@ -4444,16 +4527,16 @@
         <v>—</v>
       </c>
       <c r="M83" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N83" s="16" t="str">
-        <v>830 × 475</v>
+        <v>830 × 100</v>
       </c>
       <c r="O83" s="16" t="str">
-        <v>830 × 474,55</v>
+        <v>830 × 99,55</v>
       </c>
       <c r="P83" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="84">
@@ -4461,13 +4544,13 @@
         <v>Clóset</v>
       </c>
       <c r="B84" s="16" t="str">
-        <v>C3-007</v>
+        <v>C3-006</v>
       </c>
       <c r="C84" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D84" s="17" t="str">
-        <v>Refuerzo frontal de maletero</v>
+        <v>Piso de maletero</v>
       </c>
       <c r="E84" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4479,7 +4562,7 @@
         <v>830</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="I84" s="16" t="str">
         <v>F</v>
@@ -4494,16 +4577,16 @@
         <v>—</v>
       </c>
       <c r="M84" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N84" s="16" t="str">
-        <v>830 × 80</v>
+        <v>830 × 475</v>
       </c>
       <c r="O84" s="16" t="str">
-        <v>830 × 79,55</v>
+        <v>830 × 474,55</v>
       </c>
       <c r="P84" s="17" t="str">
-        <v>Si no la cantean: cortar a 830 × 79.55 y cantear en el armado.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="85">
@@ -4511,13 +4594,13 @@
         <v>Clóset</v>
       </c>
       <c r="B85" s="16" t="str">
-        <v>C3-008</v>
+        <v>C3-007</v>
       </c>
       <c r="C85" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D85" s="17" t="str">
-        <v>Refuerzo trasero de maletero</v>
+        <v>Refuerzo frontal de maletero</v>
       </c>
       <c r="E85" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4529,7 +4612,7 @@
         <v>830</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I85" s="16" t="str">
         <v>F</v>
@@ -4547,13 +4630,13 @@
         <v>Pequeña</v>
       </c>
       <c r="N85" s="16" t="str">
-        <v>830 × 100</v>
+        <v>830 × 80</v>
       </c>
       <c r="O85" s="16" t="str">
-        <v>830 × 99,55</v>
+        <v>830 × 79,55</v>
       </c>
       <c r="P85" s="17" t="str">
-        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 830 × 79.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="86">
@@ -4561,13 +4644,13 @@
         <v>Clóset</v>
       </c>
       <c r="B86" s="16" t="str">
-        <v>C3-009</v>
+        <v>C3-008</v>
       </c>
       <c r="C86" s="16" t="str">
-        <v>B2</v>
+        <v>B1</v>
       </c>
       <c r="D86" s="17" t="str">
-        <v>Piso sobre base</v>
+        <v>Refuerzo trasero de maletero</v>
       </c>
       <c r="E86" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4576,10 +4659,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>1075</v>
+        <v>830</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>560</v>
+        <v>100</v>
       </c>
       <c r="I86" s="16" t="str">
         <v>F</v>
@@ -4588,22 +4671,22 @@
         <v>—</v>
       </c>
       <c r="K86" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L86" s="16" t="str">
         <v>—</v>
       </c>
       <c r="M86" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N86" s="16" t="str">
-        <v>1075 × 560</v>
+        <v>830 × 100</v>
       </c>
       <c r="O86" s="16" t="str">
-        <v>1074,55 × 559,55</v>
+        <v>830 × 99,55</v>
       </c>
       <c r="P86" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="87">
@@ -4611,13 +4694,13 @@
         <v>Clóset</v>
       </c>
       <c r="B87" s="16" t="str">
-        <v>C3-010</v>
+        <v>C3-009</v>
       </c>
       <c r="C87" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D87" s="17" t="str">
-        <v>Tapa superior</v>
+        <v>Piso sobre base</v>
       </c>
       <c r="E87" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4629,7 +4712,7 @@
         <v>1075</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>505</v>
+        <v>560</v>
       </c>
       <c r="I87" s="16" t="str">
         <v>F</v>
@@ -4638,7 +4721,7 @@
         <v>—</v>
       </c>
       <c r="K87" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="L87" s="16" t="str">
         <v>—</v>
@@ -4647,10 +4730,10 @@
         <v>Normal</v>
       </c>
       <c r="N87" s="16" t="str">
-        <v>1075 × 505</v>
+        <v>1075 × 560</v>
       </c>
       <c r="O87" s="16" t="str">
-        <v>1075 × 504,55</v>
+        <v>1074,55 × 559,55</v>
       </c>
       <c r="P87" s="17" t="str">
         <v>—</v>
@@ -4661,13 +4744,13 @@
         <v>Clóset</v>
       </c>
       <c r="B88" s="16" t="str">
-        <v>C3-026</v>
+        <v>C3-010</v>
       </c>
       <c r="C88" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D88" s="17" t="str">
-        <v>Amarre posterior superior derecho</v>
+        <v>Tapa superior</v>
       </c>
       <c r="E88" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4679,7 +4762,7 @@
         <v>1075</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>100</v>
+        <v>505</v>
       </c>
       <c r="I88" s="16" t="str">
         <v>F</v>
@@ -4694,16 +4777,16 @@
         <v>—</v>
       </c>
       <c r="M88" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N88" s="16" t="str">
-        <v>1075 × 100</v>
+        <v>1075 × 505</v>
       </c>
       <c r="O88" s="16" t="str">
-        <v>1075 × 99,55</v>
+        <v>1075 × 504,55</v>
       </c>
       <c r="P88" s="17" t="str">
-        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="89">
@@ -4711,13 +4794,13 @@
         <v>Clóset</v>
       </c>
       <c r="B89" s="16" t="str">
-        <v>C3-012</v>
+        <v>C3-026</v>
       </c>
       <c r="C89" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D89" s="17" t="str">
-        <v>Piso de maletero</v>
+        <v>Amarre posterior superior derecho</v>
       </c>
       <c r="E89" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4729,7 +4812,7 @@
         <v>1075</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>475</v>
+        <v>100</v>
       </c>
       <c r="I89" s="16" t="str">
         <v>F</v>
@@ -4744,16 +4827,16 @@
         <v>—</v>
       </c>
       <c r="M89" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N89" s="16" t="str">
-        <v>1075 × 475</v>
+        <v>1075 × 100</v>
       </c>
       <c r="O89" s="16" t="str">
-        <v>1075 × 474,55</v>
+        <v>1075 × 99,55</v>
       </c>
       <c r="P89" s="17" t="str">
-        <v>—</v>
+        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
     <row r="90">
@@ -4761,13 +4844,13 @@
         <v>Clóset</v>
       </c>
       <c r="B90" s="16" t="str">
-        <v>C3-013</v>
+        <v>C3-012</v>
       </c>
       <c r="C90" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D90" s="17" t="str">
-        <v>Refuerzo frontal de maletero</v>
+        <v>Piso de maletero</v>
       </c>
       <c r="E90" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4779,7 +4862,7 @@
         <v>1075</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="I90" s="16" t="str">
         <v>F</v>
@@ -4794,16 +4877,16 @@
         <v>—</v>
       </c>
       <c r="M90" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N90" s="16" t="str">
-        <v>1075 × 80</v>
+        <v>1075 × 475</v>
       </c>
       <c r="O90" s="16" t="str">
-        <v>1075 × 79,55</v>
+        <v>1075 × 474,55</v>
       </c>
       <c r="P90" s="17" t="str">
-        <v>Si no la cantean: cortar a 1075 × 79.55 y cantear en el armado.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="91">
@@ -4811,13 +4894,13 @@
         <v>Clóset</v>
       </c>
       <c r="B91" s="16" t="str">
-        <v>C3-014</v>
+        <v>C3-013</v>
       </c>
       <c r="C91" s="16" t="str">
         <v>B2</v>
       </c>
       <c r="D91" s="17" t="str">
-        <v>Refuerzo trasero de maletero</v>
+        <v>Refuerzo frontal de maletero</v>
       </c>
       <c r="E91" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -4829,7 +4912,7 @@
         <v>1075</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I91" s="16" t="str">
         <v>F</v>
@@ -4847,13 +4930,13 @@
         <v>Pequeña</v>
       </c>
       <c r="N91" s="16" t="str">
-        <v>1075 × 100</v>
+        <v>1075 × 80</v>
       </c>
       <c r="O91" s="16" t="str">
-        <v>1075 × 99,55</v>
+        <v>1075 × 79,55</v>
       </c>
       <c r="P91" s="17" t="str">
-        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 1075 × 79.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="92">
@@ -4861,49 +4944,49 @@
         <v>Clóset</v>
       </c>
       <c r="B92" s="16" t="str">
-        <v>C3-015</v>
+        <v>C3-014</v>
       </c>
       <c r="C92" s="16" t="str">
-        <v>B1</v>
+        <v>B2</v>
       </c>
       <c r="D92" s="17" t="str">
-        <v>Frente de cajón</v>
+        <v>Refuerzo trasero de maletero</v>
       </c>
       <c r="E92" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F92" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" s="16" t="n">
-        <v>824</v>
+        <v>1075</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="I92" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J92" s="16" t="str">
-        <v>R</v>
+        <v>—</v>
       </c>
       <c r="K92" s="16" t="str">
-        <v>R</v>
+        <v>—</v>
       </c>
       <c r="L92" s="16" t="str">
-        <v>R</v>
+        <v>—</v>
       </c>
       <c r="M92" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N92" s="16" t="str">
-        <v>824 × 210</v>
+        <v>1075 × 100</v>
       </c>
       <c r="O92" s="16" t="str">
-        <v>820 × 206</v>
+        <v>1075 × 99,55</v>
       </c>
       <c r="P92" s="17" t="str">
-        <v>Veta horizontal: frente de 824 de ancho, queda detrás de las hojas.</v>
+        <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="93">
@@ -4911,49 +4994,49 @@
         <v>Clóset</v>
       </c>
       <c r="B93" s="16" t="str">
-        <v>C3-016</v>
+        <v>C3-015</v>
       </c>
       <c r="C93" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D93" s="17" t="str">
-        <v>Costado de cajón</v>
+        <v>Frente de cajón</v>
       </c>
       <c r="E93" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G93" s="16" t="n">
-        <v>450</v>
+        <v>824</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="I93" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J93" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="K93" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="L93" s="16" t="str">
-        <v>—</v>
+        <v>R</v>
       </c>
       <c r="M93" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N93" s="16" t="str">
-        <v>450 × 155</v>
+        <v>824 × 210</v>
       </c>
       <c r="O93" s="16" t="str">
-        <v>449,55 × 154,55</v>
+        <v>820 × 206</v>
       </c>
       <c r="P93" s="17" t="str">
-        <v>—</v>
+        <v>Veta horizontal: frente de 824 de ancho, queda detrás de las hojas.</v>
       </c>
     </row>
     <row r="94">
@@ -4961,25 +5044,25 @@
         <v>Clóset</v>
       </c>
       <c r="B94" s="16" t="str">
-        <v>C3-017</v>
+        <v>C3-016</v>
       </c>
       <c r="C94" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D94" s="17" t="str">
-        <v>Base aplicada de cajón</v>
+        <v>Costado de cajón</v>
       </c>
       <c r="E94" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F94" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G94" s="16" t="n">
-        <v>803</v>
+        <v>450</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>450</v>
+        <v>155</v>
       </c>
       <c r="I94" s="16" t="str">
         <v>F</v>
@@ -4991,16 +5074,16 @@
         <v>F</v>
       </c>
       <c r="L94" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M94" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N94" s="16" t="str">
-        <v>803 × 450</v>
+        <v>450 × 155</v>
       </c>
       <c r="O94" s="16" t="str">
-        <v>802,1 × 449,55</v>
+        <v>449,55 × 154,55</v>
       </c>
       <c r="P94" s="17" t="str">
         <v>—</v>
@@ -5011,25 +5094,25 @@
         <v>Clóset</v>
       </c>
       <c r="B95" s="16" t="str">
-        <v>C3-018</v>
+        <v>C3-017</v>
       </c>
       <c r="C95" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D95" s="17" t="str">
-        <v>Frente / trasero interior de cajón</v>
+        <v>Base aplicada de cajón</v>
       </c>
       <c r="E95" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G95" s="16" t="n">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>155</v>
+        <v>450</v>
       </c>
       <c r="I95" s="16" t="str">
         <v>F</v>
@@ -5038,19 +5121,19 @@
         <v>—</v>
       </c>
       <c r="K95" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="L95" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="M95" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N95" s="16" t="str">
-        <v>773 × 155</v>
+        <v>803 × 450</v>
       </c>
       <c r="O95" s="16" t="str">
-        <v>773 × 154,55</v>
+        <v>802,1 × 449,55</v>
       </c>
       <c r="P95" s="17" t="str">
         <v>—</v>
@@ -5061,25 +5144,25 @@
         <v>Clóset</v>
       </c>
       <c r="B96" s="16" t="str">
-        <v>C3-019</v>
+        <v>C3-018</v>
       </c>
       <c r="C96" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D96" s="17" t="str">
-        <v>Refuerzo bajo base de cajón</v>
+        <v>Frente / trasero interior de cajón</v>
       </c>
       <c r="E96" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F96" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G96" s="16" t="n">
-        <v>803</v>
+        <v>773</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="I96" s="16" t="str">
         <v>F</v>
@@ -5088,22 +5171,22 @@
         <v>—</v>
       </c>
       <c r="K96" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="L96" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="M96" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N96" s="16" t="str">
-        <v>803 × 40</v>
+        <v>773 × 155</v>
       </c>
       <c r="O96" s="16" t="str">
-        <v>802,1 × 39,55</v>
+        <v>773 × 154,55</v>
       </c>
       <c r="P96" s="17" t="str">
-        <v>Si no la cantean: cortar a 802.1 × 39.55 y cantear en el armado.</v>
+        <v>—</v>
       </c>
     </row>
     <row r="97">
@@ -5111,31 +5194,31 @@
         <v>Clóset</v>
       </c>
       <c r="B97" s="16" t="str">
-        <v>C3-020</v>
+        <v>C3-019</v>
       </c>
       <c r="C97" s="16" t="str">
-        <v>BASE</v>
+        <v>B1</v>
       </c>
       <c r="D97" s="17" t="str">
-        <v>Zócalo frontal</v>
+        <v>Refuerzo bajo base de cajón</v>
       </c>
       <c r="E97" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" s="16" t="n">
-        <v>1950</v>
+        <v>803</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="I97" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J97" s="16" t="str">
-        <v>F</v>
+        <v>—</v>
       </c>
       <c r="K97" s="16" t="str">
         <v>F</v>
@@ -5147,13 +5230,13 @@
         <v>Pequeña</v>
       </c>
       <c r="N97" s="16" t="str">
-        <v>1950 × 92</v>
+        <v>803 × 40</v>
       </c>
       <c r="O97" s="16" t="str">
-        <v>1949,1 × 91,1</v>
+        <v>802,1 × 39,55</v>
       </c>
       <c r="P97" s="17" t="str">
-        <v>Si no la cantean: cortar a 1949.1 × 91.1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 802.1 × 39.55 y cantear en el armado.</v>
       </c>
     </row>
     <row r="98">
@@ -5161,13 +5244,13 @@
         <v>Clóset</v>
       </c>
       <c r="B98" s="16" t="str">
-        <v>C3-021</v>
+        <v>C3-020</v>
       </c>
       <c r="C98" s="16" t="str">
         <v>BASE</v>
       </c>
       <c r="D98" s="17" t="str">
-        <v>Travesaño trasero de base</v>
+        <v>Zócalo frontal</v>
       </c>
       <c r="E98" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -5179,7 +5262,7 @@
         <v>1950</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I98" s="16" t="str">
         <v>F</v>
@@ -5197,13 +5280,13 @@
         <v>Pequeña</v>
       </c>
       <c r="N98" s="16" t="str">
-        <v>1950 × 80</v>
+        <v>1950 × 92</v>
       </c>
       <c r="O98" s="16" t="str">
-        <v>1949,1 × 79,1</v>
+        <v>1949,1 × 91,1</v>
       </c>
       <c r="P98" s="17" t="str">
-        <v>Si no la cantean: cortar a 1949.1 × 79.1 y cantear en el armado.</v>
+        <v>Si no la cantean: cortar a 1949.1 × 91.1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="99">
@@ -5211,22 +5294,22 @@
         <v>Clóset</v>
       </c>
       <c r="B99" s="16" t="str">
-        <v>C3-022</v>
+        <v>C3-021</v>
       </c>
       <c r="C99" s="16" t="str">
         <v>BASE</v>
       </c>
       <c r="D99" s="17" t="str">
-        <v>Travesaño de base</v>
+        <v>Travesaño trasero de base</v>
       </c>
       <c r="E99" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G99" s="16" t="n">
-        <v>480</v>
+        <v>1950</v>
       </c>
       <c r="H99" s="16" t="n">
         <v>80</v>
@@ -5247,63 +5330,63 @@
         <v>Pequeña</v>
       </c>
       <c r="N99" s="16" t="str">
-        <v>480 × 80</v>
+        <v>1950 × 80</v>
       </c>
       <c r="O99" s="16" t="str">
-        <v>479,1 × 79,1</v>
+        <v>1949,1 × 79,1</v>
       </c>
       <c r="P99" s="17" t="str">
-        <v>Si no la cantean: cortar a 479.1 × 79.1 y cantear en el armado.</v>
-      </c>
-    </row>
-    <row r="100" ht="57.599998474121094">
+        <v>Si no la cantean: cortar a 1949.1 × 79.1 y cantear en el armado.</v>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" s="16" t="str">
         <v>Clóset</v>
       </c>
       <c r="B100" s="16" t="str">
-        <v>C3-023</v>
+        <v>C3-022</v>
       </c>
       <c r="C100" s="16" t="str">
-        <v>PUERTAS</v>
+        <v>BASE</v>
       </c>
       <c r="D100" s="17" t="str">
-        <v>Hoja corrediza RH15</v>
+        <v>Travesaño de base</v>
       </c>
       <c r="E100" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F100" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G100" s="16" t="n">
-        <v>2195</v>
+        <v>480</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>975</v>
+        <v>80</v>
       </c>
       <c r="I100" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J100" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="K100" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L100" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M100" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N100" s="16" t="str">
-        <v>2175 × 975</v>
+        <v>480 × 80</v>
       </c>
       <c r="O100" s="16" t="str">
-        <v>2191 × 971</v>
+        <v>479,1 × 79,1</v>
       </c>
       <c r="P100" s="17" t="str">
-        <v>Pedida 20 mm más alta (2195 en vez de 2175): en el armado, con el riel y los carros puestos, recortar el borde superior —tapado por la solapa— hasta que la guía inferior sujete la hoja. Nunca debe quedar corta.</v>
+        <v>Si no la cantean: cortar a 479.1 × 79.1 y cantear en el armado.</v>
       </c>
     </row>
     <row r="101">
@@ -5311,63 +5394,63 @@
         <v>Clóset</v>
       </c>
       <c r="B101" s="16" t="str">
-        <v>C3-024</v>
+        <v>C3-023</v>
       </c>
       <c r="C101" s="16" t="str">
-        <v>EST</v>
+        <v>PUERTAS</v>
       </c>
       <c r="D101" s="17" t="str">
-        <v>Solapa frontal</v>
+        <v>Hoja corrediza RH15</v>
       </c>
       <c r="E101" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="16" t="n">
-        <v>1950</v>
+        <v>2195</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>120</v>
+        <v>975</v>
       </c>
       <c r="I101" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J101" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="K101" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="L101" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="M101" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N101" s="16" t="str">
-        <v>1950 × 120</v>
+        <v>2175 × 975</v>
       </c>
       <c r="O101" s="16" t="str">
-        <v>1949,1 × 119,1</v>
+        <v>2191 × 971</v>
       </c>
       <c r="P101" s="17" t="str">
-        <v>—</v>
-      </c>
-    </row>
-    <row r="102" ht="28.799999237060547">
+        <v>Pedida 20 mm más alta (2195 en vez de 2175): en el armado, con el riel y los carros puestos, recortar el borde superior —tapado por la solapa— hasta que la guía inferior sujete la hoja. Nunca debe quedar corta.</v>
+      </c>
+    </row>
+    <row r="102">
       <c r="A102" s="16" t="str">
         <v>Clóset</v>
       </c>
       <c r="B102" s="16" t="str">
-        <v>C3-027</v>
+        <v>C3-024</v>
       </c>
       <c r="C102" s="16" t="str">
-        <v>B2</v>
+        <v>EST</v>
       </c>
       <c r="D102" s="17" t="str">
-        <v>Montante posterior derecho</v>
+        <v>Solapa frontal</v>
       </c>
       <c r="E102" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -5376,48 +5459,48 @@
         <v>1</v>
       </c>
       <c r="G102" s="16" t="n">
-        <v>2050</v>
+        <v>1950</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I102" s="16" t="str">
         <v>F</v>
       </c>
       <c r="J102" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="K102" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="L102" s="16" t="str">
-        <v>—</v>
+        <v>F</v>
       </c>
       <c r="M102" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N102" s="16" t="str">
-        <v>2050 × 100</v>
+        <v>1950 × 120</v>
       </c>
       <c r="O102" s="16" t="str">
-        <v>2050 × 99,55</v>
+        <v>1949,1 × 119,1</v>
       </c>
       <c r="P102" s="17" t="str">
-        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
-      </c>
-    </row>
-    <row r="103" ht="28.799999237060547">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="16" t="str">
         <v>Clóset</v>
       </c>
       <c r="B103" s="16" t="str">
-        <v>C3-028</v>
+        <v>C3-027</v>
       </c>
       <c r="C103" s="16" t="str">
-        <v>B1</v>
+        <v>B2</v>
       </c>
       <c r="D103" s="17" t="str">
-        <v>Montante posterior izquierdo</v>
+        <v>Montante posterior derecho</v>
       </c>
       <c r="E103" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -5453,21 +5536,21 @@
         <v>2050 × 99,55</v>
       </c>
       <c r="P103" s="17" t="str">
-        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
-      </c>
-    </row>
-    <row r="104" ht="57.599998474121094">
+        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" s="16" t="str">
         <v>Clóset</v>
       </c>
       <c r="B104" s="16" t="str">
-        <v>C3-029</v>
+        <v>C3-028</v>
       </c>
       <c r="C104" s="16" t="str">
         <v>B1</v>
       </c>
       <c r="D104" s="17" t="str">
-        <v>Amarre posterior inferior izquierdo</v>
+        <v>Montante posterior izquierdo</v>
       </c>
       <c r="E104" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -5476,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="16" t="n">
-        <v>830</v>
+        <v>2050</v>
       </c>
       <c r="H104" s="16" t="n">
         <v>100</v>
@@ -5497,27 +5580,27 @@
         <v>Pequeña</v>
       </c>
       <c r="N104" s="16" t="str">
-        <v>830 × 100</v>
+        <v>2050 × 100</v>
       </c>
       <c r="O104" s="16" t="str">
-        <v>830 × 99,55</v>
+        <v>2050 × 99,55</v>
       </c>
       <c r="P104" s="17" t="str">
-        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
-      </c>
-    </row>
-    <row r="105" ht="57.599998474121094">
+        <v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" s="16" t="str">
         <v>Clóset</v>
       </c>
       <c r="B105" s="16" t="str">
-        <v>C3-030</v>
+        <v>C3-029</v>
       </c>
       <c r="C105" s="16" t="str">
-        <v>B2</v>
+        <v>B1</v>
       </c>
       <c r="D105" s="17" t="str">
-        <v>Amarre posterior inferior derecho</v>
+        <v>Amarre posterior inferior izquierdo</v>
       </c>
       <c r="E105" s="16" t="str">
         <v>RH15 Cartagena 15 mm</v>
@@ -5526,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="16" t="n">
-        <v>1075</v>
+        <v>830</v>
       </c>
       <c r="H105" s="16" t="n">
         <v>100</v>
@@ -5547,86 +5630,86 @@
         <v>Pequeña</v>
       </c>
       <c r="N105" s="16" t="str">
+        <v>830 × 100</v>
+      </c>
+      <c r="O105" s="16" t="str">
+        <v>830 × 99,55</v>
+      </c>
+      <c r="P105" s="17" t="str">
+        <v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="str">
+        <v>Clóset</v>
+      </c>
+      <c r="B106" s="16" t="str">
+        <v>C3-030</v>
+      </c>
+      <c r="C106" s="16" t="str">
+        <v>B2</v>
+      </c>
+      <c r="D106" s="17" t="str">
+        <v>Amarre posterior inferior derecho</v>
+      </c>
+      <c r="E106" s="16" t="str">
+        <v>RH15 Cartagena 15 mm</v>
+      </c>
+      <c r="F106" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="16" t="n">
+        <v>1075</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I106" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="J106" s="16" t="str">
+        <v>—</v>
+      </c>
+      <c r="K106" s="16" t="str">
+        <v>—</v>
+      </c>
+      <c r="L106" s="16" t="str">
+        <v>—</v>
+      </c>
+      <c r="M106" s="16" t="str">
+        <v>Pequeña</v>
+      </c>
+      <c r="N106" s="16" t="str">
         <v>1075 × 100</v>
       </c>
-      <c r="O105" s="16" t="str">
+      <c r="O106" s="16" t="str">
         <v>1075 × 99,55</v>
       </c>
-      <c r="P105" s="17" t="str">
+      <c r="P106" s="17" t="str">
         <v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</v>
       </c>
     </row>
-    <row r="106" ht="57.599998474121094">
-      <c r="A106" s="16" t="str">
-        <v>Baño</v>
-      </c>
-      <c r="B106" s="16" t="str">
-        <v>B01</v>
-      </c>
-      <c r="C106" s="16" t="str">
-        <v>BAJO</v>
-      </c>
-      <c r="D106" s="17" t="str">
-        <v>Lateral</v>
-      </c>
-      <c r="E106" s="16" t="str">
-        <v>RH15 Cartagena</v>
-      </c>
-      <c r="F106" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G106" s="16" t="n">
-        <v>470</v>
-      </c>
-      <c r="H106" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="I106" s="16" t="str">
-        <v>F</v>
-      </c>
-      <c r="J106" s="16" t="str">
-        <v>F</v>
-      </c>
-      <c r="K106" s="16" t="str">
-        <v>F</v>
-      </c>
-      <c r="L106" s="16" t="str">
-        <v>F</v>
-      </c>
-      <c r="M106" s="16" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N106" s="16" t="str">
-        <v>470 × 450</v>
-      </c>
-      <c r="O106" s="16" t="str">
-        <v>469,1 × 449,1</v>
-      </c>
-      <c r="P106" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="107" ht="100.80000305175781">
+    <row r="107">
       <c r="A107" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B107" s="16" t="str">
-        <v>B02</v>
+        <v>B01</v>
       </c>
       <c r="C107" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D107" s="17" t="str">
-        <v>Piso</v>
+        <v>Lateral</v>
       </c>
       <c r="E107" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" s="16" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="H107" s="16" t="n">
         <v>450</v>
@@ -5647,27 +5730,27 @@
         <v>Normal</v>
       </c>
       <c r="N107" s="16" t="str">
-        <v>490 × 450</v>
+        <v>470 × 450</v>
       </c>
       <c r="O107" s="16" t="str">
-        <v>489,1 × 449,1</v>
+        <v>469,1 × 449,1</v>
       </c>
       <c r="P107" s="17" t="str">
         <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
-    <row r="108" ht="43.20000076293945">
+    <row r="108">
       <c r="A108" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B108" s="16" t="str">
-        <v>B03</v>
+        <v>B02</v>
       </c>
       <c r="C108" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D108" s="17" t="str">
-        <v>Entrepaño retranqueado con reserva de sifón</v>
+        <v>Piso</v>
       </c>
       <c r="E108" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5679,7 +5762,7 @@
         <v>490</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="I108" s="16" t="str">
         <v>F</v>
@@ -5697,39 +5780,39 @@
         <v>Normal</v>
       </c>
       <c r="N108" s="16" t="str">
-        <v>490 × 405</v>
+        <v>490 × 450</v>
       </c>
       <c r="O108" s="16" t="str">
-        <v>489,1 × 404,1</v>
+        <v>489,1 × 449,1</v>
       </c>
       <c r="P108" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="109" ht="28.799999237060547">
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="109">
       <c r="A109" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B109" s="16" t="str">
-        <v>B04</v>
+        <v>B03</v>
       </c>
       <c r="C109" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D109" s="17" t="str">
-        <v>Travesaño trasero superior lateral</v>
+        <v>Entrepaño retranqueado con reserva de sifón</v>
       </c>
       <c r="E109" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109" s="16" t="n">
-        <v>195</v>
+        <v>490</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="I109" s="16" t="str">
         <v>F</v>
@@ -5744,39 +5827,39 @@
         <v>F</v>
       </c>
       <c r="M109" s="16" t="str">
-        <v>Pequeña</v>
+        <v>Normal</v>
       </c>
       <c r="N109" s="16" t="str">
-        <v>195 × 80</v>
+        <v>490 × 405</v>
       </c>
       <c r="O109" s="16" t="str">
-        <v>194,1 × 79,1</v>
+        <v>489,1 × 404,1</v>
       </c>
       <c r="P109" s="17" t="str">
-        <v>Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="110" ht="43.20000076293945">
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="110">
       <c r="A110" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B110" s="16" t="str">
-        <v>B05</v>
+        <v>B04</v>
       </c>
       <c r="C110" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D110" s="17" t="str">
-        <v>Travesaño trasero inferior</v>
+        <v>Travesaño trasero superior lateral</v>
       </c>
       <c r="E110" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F110" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="16" t="n">
-        <v>490</v>
+        <v>195</v>
       </c>
       <c r="H110" s="16" t="n">
         <v>80</v>
@@ -5797,27 +5880,27 @@
         <v>Pequeña</v>
       </c>
       <c r="N110" s="16" t="str">
-        <v>490 × 80</v>
+        <v>195 × 80</v>
       </c>
       <c r="O110" s="16" t="str">
-        <v>489,1 × 79,1</v>
+        <v>194,1 × 79,1</v>
       </c>
       <c r="P110" s="17" t="str">
-        <v>Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="111" ht="43.20000076293945">
+        <v>Si no la cantean: cortar a 194,1 × 79,1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="111">
       <c r="A111" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B111" s="16" t="str">
-        <v>B06</v>
+        <v>B05</v>
       </c>
       <c r="C111" s="16" t="str">
         <v>BAJO</v>
       </c>
       <c r="D111" s="17" t="str">
-        <v>Panel común para dos puertas: corte diagonal en armado</v>
+        <v>Travesaño trasero inferior</v>
       </c>
       <c r="E111" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5826,98 +5909,98 @@
         <v>1</v>
       </c>
       <c r="G111" s="16" t="n">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="H111" s="16" t="n">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="I111" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="J111" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="K111" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="L111" s="16" t="str">
-        <v>R</v>
+        <v>F</v>
       </c>
       <c r="M111" s="16" t="str">
-        <v>Normal</v>
+        <v>Pequeña</v>
       </c>
       <c r="N111" s="16" t="str">
-        <v>299 × 517</v>
+        <v>490 × 80</v>
       </c>
       <c r="O111" s="16" t="str">
-        <v>295 × 513</v>
+        <v>489,1 × 79,1</v>
       </c>
       <c r="P111" s="17" t="str">
-        <v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</v>
-      </c>
-    </row>
-    <row r="112" ht="43.20000076293945">
+        <v>Si no la cantean: cortar a 489,1 × 79,1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="112">
       <c r="A112" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B112" s="16" t="str">
-        <v>S01</v>
+        <v>B06</v>
       </c>
       <c r="C112" s="16" t="str">
-        <v>ESPEJO</v>
+        <v>BAJO</v>
       </c>
       <c r="D112" s="17" t="str">
-        <v>Lateral gabinete superior</v>
+        <v>Panel común para dos puertas: corte diagonal en armado</v>
       </c>
       <c r="E112" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F112" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" s="16" t="n">
-        <v>500</v>
+        <v>299</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>105</v>
+        <v>517</v>
       </c>
       <c r="I112" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="J112" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="K112" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="L112" s="16" t="str">
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="M112" s="16" t="str">
         <v>Normal</v>
       </c>
       <c r="N112" s="16" t="str">
-        <v>500 × 105</v>
+        <v>299 × 517</v>
       </c>
       <c r="O112" s="16" t="str">
-        <v>499,1 × 104,1</v>
+        <v>295 × 513</v>
       </c>
       <c r="P112" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="113" ht="43.20000076293945">
+        <v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</v>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B113" s="16" t="str">
-        <v>S02</v>
+        <v>S01</v>
       </c>
       <c r="C113" s="16" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D113" s="17" t="str">
-        <v>Piso y techo gabinete superior</v>
+        <v>Lateral gabinete superior</v>
       </c>
       <c r="E113" s="16" t="str">
         <v>RH15 Cartagena</v>
@@ -5926,7 +6009,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="16" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="H113" s="16" t="n">
         <v>105</v>
@@ -5947,36 +6030,36 @@
         <v>Normal</v>
       </c>
       <c r="N113" s="16" t="str">
-        <v>420 × 105</v>
+        <v>500 × 105</v>
       </c>
       <c r="O113" s="16" t="str">
-        <v>419,1 × 104,1</v>
+        <v>499,1 × 104,1</v>
       </c>
       <c r="P113" s="17" t="str">
-        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="114" ht="43.20000076293945">
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="114">
       <c r="A114" s="16" t="str">
         <v>Baño</v>
       </c>
       <c r="B114" s="16" t="str">
-        <v>S03</v>
+        <v>S02</v>
       </c>
       <c r="C114" s="16" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D114" s="17" t="str">
-        <v>División vertical</v>
+        <v>Piso y techo gabinete superior</v>
       </c>
       <c r="E114" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
       <c r="F114" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G114" s="16" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="H114" s="16" t="n">
         <v>105</v>
@@ -5997,163 +6080,163 @@
         <v>Normal</v>
       </c>
       <c r="N114" s="16" t="str">
+        <v>420 × 105</v>
+      </c>
+      <c r="O114" s="16" t="str">
+        <v>419,1 × 104,1</v>
+      </c>
+      <c r="P114" s="17" t="str">
+        <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B115" s="16" t="str">
+        <v>S03</v>
+      </c>
+      <c r="C115" s="16" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D115" s="17" t="str">
+        <v>División vertical</v>
+      </c>
+      <c r="E115" s="16" t="str">
+        <v>RH15 Cartagena</v>
+      </c>
+      <c r="F115" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="16" t="n">
+        <v>470</v>
+      </c>
+      <c r="H115" s="16" t="n">
+        <v>105</v>
+      </c>
+      <c r="I115" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="J115" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="K115" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="L115" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="M115" s="16" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="N115" s="16" t="str">
         <v>470 × 105</v>
       </c>
-      <c r="O114" s="16" t="str">
+      <c r="O115" s="16" t="str">
         <v>469,1 × 104,1</v>
       </c>
-      <c r="P114" s="17" t="str">
+      <c r="P115" s="17" t="str">
         <v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="13" t="str">
+    <row r="116">
+      <c r="A116" s="16" t="str">
         <v>Baño</v>
       </c>
-      <c r="B115" s="13" t="str">
+      <c r="B116" s="16" t="str">
         <v>S04</v>
       </c>
-      <c r="C115" s="13" t="str">
+      <c r="C116" s="16" t="str">
         <v>ESPEJO</v>
       </c>
-      <c r="D115" s="13" t="str">
+      <c r="D116" s="17" t="str">
         <v>Entrepaño interior izquierdo</v>
       </c>
-      <c r="E115" s="13" t="str">
+      <c r="E116" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
-      <c r="F115" s="13" t="n">
+      <c r="F116" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G115" s="13" t="n">
+      <c r="G116" s="16" t="n">
         <v>290</v>
       </c>
-      <c r="H115" s="13" t="n">
+      <c r="H116" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="I115" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="J115" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="K115" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="L115" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="M115" s="13" t="str">
+      <c r="I116" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="J116" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="K116" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="L116" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="M116" s="16" t="str">
         <v>Pequeña</v>
       </c>
-      <c r="N115" s="13" t="str">
+      <c r="N116" s="16" t="str">
         <v>290 × 100</v>
       </c>
-      <c r="O115" s="13" t="str">
+      <c r="O116" s="16" t="str">
         <v>289,1 × 99,1</v>
       </c>
-      <c r="P115" s="13" t="str">
-        <v>Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="13" t="str">
+      <c r="P116" s="17" t="str">
+        <v>Si no la cantean: cortar a 289,1 × 99,1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="str">
         <v>Baño</v>
       </c>
-      <c r="B116" s="13" t="str">
+      <c r="B117" s="16" t="str">
         <v>S05</v>
       </c>
-      <c r="C116" s="13" t="str">
+      <c r="C117" s="16" t="str">
         <v>ESPEJO</v>
       </c>
-      <c r="D116" s="13" t="str">
+      <c r="D117" s="17" t="str">
         <v>Entrepaño columna abierta derecha</v>
       </c>
-      <c r="E116" s="13" t="str">
+      <c r="E117" s="16" t="str">
         <v>RH15 Cartagena</v>
       </c>
-      <c r="F116" s="13" t="n">
+      <c r="F117" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G116" s="13" t="n">
+      <c r="G117" s="16" t="n">
         <v>115</v>
       </c>
-      <c r="H116" s="13" t="n">
+      <c r="H117" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="I116" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="J116" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="K116" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="L116" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="M116" s="13" t="str">
+      <c r="I117" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="J117" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="K117" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="L117" s="16" t="str">
+        <v>F</v>
+      </c>
+      <c r="M117" s="16" t="str">
         <v>Pequeña</v>
       </c>
-      <c r="N116" s="13" t="str">
+      <c r="N117" s="16" t="str">
         <v>115 × 100</v>
       </c>
-      <c r="O116" s="13" t="str">
+      <c r="O117" s="16" t="str">
         <v>114,1 × 99,1</v>
       </c>
-      <c r="P116" s="13" t="str">
-        <v>Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="13" t="str">
-        <v>Baño</v>
-      </c>
-      <c r="B117" s="13" t="str">
-        <v>S06</v>
-      </c>
-      <c r="C117" s="13" t="str">
-        <v>ESPEJO</v>
-      </c>
-      <c r="D117" s="13" t="str">
-        <v>Tapa RH15 portadora del espejo</v>
-      </c>
-      <c r="E117" s="13" t="str">
-        <v>RH15 Cartagena</v>
-      </c>
-      <c r="F117" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="H117" s="13" t="n">
-        <v>320</v>
-      </c>
-      <c r="I117" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="J117" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="K117" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="L117" s="13" t="str">
-        <v>F</v>
-      </c>
-      <c r="M117" s="13" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N117" s="13" t="str">
-        <v>500 × 320</v>
-      </c>
-      <c r="O117" s="13" t="str">
-        <v>499,1 × 319,1</v>
-      </c>
-      <c r="P117" s="13" t="str">
-        <v>Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      <c r="P117" s="17" t="str">
+        <v>Si no la cantean: cortar a 114,1 × 99,1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
     <row r="118">
@@ -6161,25 +6244,25 @@
         <v>Baño</v>
       </c>
       <c r="B118" s="13" t="str">
-        <v>F01</v>
+        <v>S06</v>
       </c>
       <c r="C118" s="13" t="str">
         <v>ESPEJO</v>
       </c>
       <c r="D118" s="13" t="str">
-        <v>Fondo blanco de 6 mm</v>
+        <v>Tapa RH15 portadora del espejo</v>
       </c>
       <c r="E118" s="13" t="str">
-        <v>Fondo melamina blanco RH6</v>
+        <v>RH15 Cartagena</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H118" s="13" t="n">
-        <v>446</v>
+        <v>320</v>
       </c>
       <c r="I118" s="13" t="str">
         <v>F</v>
@@ -6197,24 +6280,74 @@
         <v>Normal</v>
       </c>
       <c r="N118" s="13" t="str">
+        <v>500 × 320</v>
+      </c>
+      <c r="O118" s="13" t="str">
+        <v>499,1 × 319,1</v>
+      </c>
+      <c r="P118" s="13" t="str">
+        <v>Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="str">
+        <v>Baño</v>
+      </c>
+      <c r="B119" s="13" t="str">
+        <v>F01</v>
+      </c>
+      <c r="C119" s="13" t="str">
+        <v>ESPEJO</v>
+      </c>
+      <c r="D119" s="13" t="str">
+        <v>Fondo blanco de 6 mm</v>
+      </c>
+      <c r="E119" s="13" t="str">
+        <v>Fondo melamina blanco RH6</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="13" t="n">
+        <v>496</v>
+      </c>
+      <c r="H119" s="13" t="n">
+        <v>446</v>
+      </c>
+      <c r="I119" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="J119" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="K119" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="L119" s="13" t="str">
+        <v>F</v>
+      </c>
+      <c r="M119" s="13" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="N119" s="13" t="str">
         <v>496 × 446</v>
       </c>
-      <c r="O118" s="13" t="str">
+      <c r="O119" s="13" t="str">
         <v>495,1 × 445,1</v>
       </c>
-      <c r="P118" s="13" t="str">
+      <c r="P119" s="13" t="str">
         <v>Fondo aplicado por detrás, retranqueado 2 mm de los bordes. Reutilización de sobrantes de cocina solo se comprobará en la optimización conjunta final. No soporta el anclaje del gabinete. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:P118"/>
+  <autoFilter ref="A6:P119"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" customWidth="1"/>
     <x:col min="2" max="2" width="8" customWidth="1"/>
@@ -6222,7 +6355,7 @@
     <x:col min="4" max="4" width="120" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Encaje conjunto en láminas · propuesta de factibilidad</x:v>
       </x:c>
@@ -6260,7 +6393,7 @@
         <x:v>Clóset C3-023, Clóset C3-023, Clóset C3-024, Cocina P016, Cocina P011, Cocina P040, Cocina P043, Clóset C3-019, Clóset C3-019, Baño B04, Baño B04, Cocina P003, Cocina P003</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="28.799999237060547">
+    <x:row r="8">
       <x:c r="A8" s="13" t="str">
         <x:v>RH15</x:v>
       </x:c>
@@ -6310,13 +6443,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:v>0.883</x:v>
+        <x:v>0.905</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>Clóset C3-006, Clóset C3-017, Clóset C3-017, Cocina P029, Cocina P017, Cocina P007, Cocina P009, Cocina P056, Cocina P057, Cocina P039, Cocina P039, Cocina P050, Cocina P050, Cocina P058, Cocina P031, Cocina P002, Cocina P025, Cocina P008, Cocina P061, Cocina P010, Cocina P018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="43.20000076293945">
+        <x:v>Clóset C3-006, Clóset C3-017, Clóset C3-017, Cocina P029, Cocina P017, Cocina P007, Cocina P009, Cocina P049, Cocina P056, Cocina P057, Cocina P039, Cocina P039, Cocina P031, Cocina P034, Cocina P035, Cocina P066, Cocina P002, Clóset C3-016, Cocina P025, Cocina P008, Cocina P061, Cocina P018, Cocina P076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
       <x:c r="A12" s="13" t="str">
         <x:v>RH15</x:v>
       </x:c>
@@ -6324,13 +6457,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="18" t="n">
-        <x:v>0.784</x:v>
+        <x:v>0.877</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>Cocina P058, Cocina P065, Cocina P065, Cocina P059, Cocina P054, Baño B01, Baño B01, Cocina P049, Cocina P034, Cocina P051, Cocina P052, Baño B03, Cocina P046, Cocina P047, Cocina P020, Cocina P035, Baño B06, Cocina P036, Cocina P055, Cocina P055, Clóset C3-016, Clóset C3-016, Clóset C3-016, Baño S01, Baño S03, Baño S04, Baño S04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="43.20000076293945">
+        <x:v>Cocina P050, Cocina P050, Cocina P058, Cocina P058, Cocina P065, Cocina P065, Cocina P059, Cocina P054, Baño B01, Baño B01, Cocina P051, Cocina P052, Baño B03, Cocina P075, Cocina P046, Cocina P047, Cocina P020, Cocina P021, Baño S06, Baño B06, Cocina P045, Cocina P055, Clóset C3-016, Clóset C3-016, Baño S01, Baño S02, Baño S04, Cocina P076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
       <x:c r="A13" s="13" t="str">
         <x:v>RH15</x:v>
       </x:c>
@@ -6338,13 +6471,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="18" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.804</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>Clóset C3-027, Clóset C3-028, Clóset C3-020, Cocina P021, Clóset C3-015, Clóset C3-015, Clóset C3-015, Baño S06, Cocina P044, Cocina P005, Cocina P038, Cocina P038, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Cocina P066, Cocina P067, Cocina P045, Cocina P045, Cocina P069, Clóset C3-016, Clóset C3-016, Clóset C3-016, Cocina P025, Cocina P014, Cocina P014, Baño S02, Baño S02, Cocina P019, Cocina P019, Cocina P032, Cocina P032</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="57.599998474121094">
+        <x:v>Clóset C3-027, Clóset C3-028, Clóset C3-020, Clóset C3-015, Clóset C3-015, Clóset C3-015, Cocina P045, Cocina P044, Cocina P005, Cocina P038, Cocina P038, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Clóset C3-018, Cocina P067, Cocina P036, Cocina P069, Clóset C3-026, Clóset C3-014, Clóset C3-030, Cocina P055, Clóset C3-013, Clóset C3-025, Clóset C3-008, Clóset C3-029, Clóset C3-016, Clóset C3-016, Clóset C3-016, Cocina P025, Cocina P014, Cocina P014, Baño S03, Baño S02, Cocina P032, Cocina P032, Baño S04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
       <x:c r="A14" s="13" t="str">
         <x:v>RH15</x:v>
       </x:c>
@@ -6352,10 +6485,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="18" t="n">
-        <x:v>0.228</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Clóset C3-021, Clóset C3-026, Clóset C3-014, Clóset C3-030, Clóset C3-013, Clóset C3-025, Clóset C3-008, Clóset C3-029, Clóset C3-007, Cocina P018, Cocina P060, Baño B05, Clóset C3-022, Clóset C3-022, Clóset C3-022, Cocina P071, Clóset C3-019</x:v>
+        <x:v>Clóset C3-021, Clóset C3-007, Cocina P010, Cocina P019, Cocina P019, Cocina P018, Cocina P060, Baño B05, Clóset C3-022, Clóset C3-022, Clóset C3-022, Clóset C3-019</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6366,10 +6499,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="18" t="n">
-        <x:v>0.639</x:v>
+        <x:v>0.651</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>Cocina P026, Cocina P015, Cocina P062, Cocina P053, Cocina P033, Cocina P068, Baño F01, Cocina P048, Cocina P004, Cocina P042</x:v>
+        <x:v>Cocina P026, Cocina P015, Cocina P062, Cocina P053, Cocina P033, Cocina P068, Cocina P048, Baño F01, Cocina P004, Cocina P042</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6379,7 +6512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" customWidth="1"/>
     <x:col min="2" max="2" width="22" customWidth="1"/>
@@ -6387,7 +6520,7 @@
     <x:col min="4" max="4" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Canto conjunto</x:v>
       </x:c>
@@ -6419,7 +6552,7 @@
         <x:v>Cocina</x:v>
       </x:c>
       <x:c r="C7" s="13" t="n">
-        <x:v>30.137</x:v>
+        <x:v>30.337</x:v>
       </x:c>
       <x:c r="D7" s="13" t="n">
         <x:v>62</x:v>
@@ -6461,7 +6594,7 @@
         <x:v>Total · comprar 61 m</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
-        <x:v>50.573</x:v>
+        <x:v>50.773</x:v>
       </x:c>
       <x:c r="D10" s="14" t="n">
         <x:v>86</x:v>
@@ -6475,10 +6608,10 @@
         <x:v>Cocina</x:v>
       </x:c>
       <x:c r="C12" s="13" t="n">
-        <x:v>68.018</x:v>
+        <x:v>71.408</x:v>
       </x:c>
       <x:c r="D12" s="13" t="n">
-        <x:v>150</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6514,13 +6647,13 @@
         <x:v>Flexible 0,45 mm</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Total · comprar 181 m</x:v>
+        <x:v>Total · comprar 186 m</x:v>
       </x:c>
       <x:c r="C15" s="14" t="n">
-        <x:v>149.206</x:v>
+        <x:v>152.596</x:v>
       </x:c>
       <x:c r="D15" s="14" t="n">
-        <x:v>306</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6530,7 +6663,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" customWidth="1"/>
     <x:col min="2" max="2" width="46" customWidth="1"/>
@@ -6542,7 +6675,7 @@
     <x:col min="8" max="8" width="80" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Compras consolidadas</x:v>
       </x:c>
@@ -6552,7 +6685,7 @@
         <x:v>Precios de referencia de los Excel de cada mueble. «cotizar» = sin precio; no equivale a cero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="28.799999237060547">
+    <x:row r="9">
       <x:c r="A9" s="12" t="str">
         <x:v>Grupo</x:v>
       </x:c>
@@ -6578,7 +6711,7 @@
         <x:v>Nota</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="28.799999237060547">
+    <x:row r="10">
       <x:c r="A10" s="13" t="str">
         <x:v>Tableros y cantos</x:v>
       </x:c>
@@ -6598,11 +6731,11 @@
         <x:v>365872</x:v>
       </x:c>
       <x:c r="G10" s="19" t="n">
-        <x:f t="shared" ref="G10:G41" si="0">IF(AND(ISNUMBER(D10),ISNUMBER(F10)),D10*F10,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D10),ISNUMBER(F10)),D10*F10,"Por cotizar")</x:f>
         <x:v>2926976</x:v>
       </x:c>
       <x:c r="H10" s="17" t="str">
-        <x:v>Encaje conjunto de las piezas RH15 de los tres muebles en 8 láminas (hoja Láminas). Por separado serían 9.</x:v>
+        <x:v>Encaje conjunto de las piezas RH15 de los tres muebles en 8 láminas (hoja Láminas). El total por separado se muestra en Resumen.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6625,7 +6758,7 @@
         <x:v>212534</x:v>
       </x:c>
       <x:c r="G11" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D11),ISNUMBER(F11)),D11*F11,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D11),ISNUMBER(F11)),D11*F11,"Por cotizar")</x:f>
         <x:v>212534</x:v>
       </x:c>
       <x:c r="H11" s="17" t="str">
@@ -6652,11 +6785,11 @@
         <x:v>531600</x:v>
       </x:c>
       <x:c r="G12" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D12),ISNUMBER(F12)),D12*F12,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D12),ISNUMBER(F12)),D12*F12,"Por cotizar")</x:f>
         <x:v>531600</x:v>
       </x:c>
       <x:c r="H12" s="17" t="str">
-        <x:v>Necesario 61 m: 50,6 m netos + 5 cm por borde (86 bordes) + 10 %.</x:v>
+        <x:v>Necesario 61 m: 50,8 m netos + 5 cm por borde (86 bordes) + 10 %.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6679,14 +6812,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G13" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D13),ISNUMBER(F13)),D13*F13,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D13),ISNUMBER(F13)),D13*F13,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H13" s="17" t="str">
         <x:v>Complemento del rollo de 100 m; se compra suelto en la sucursal.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="28.799999237060547">
+    <x:row r="14">
       <x:c r="A14" s="13" t="str">
         <x:v>Tableros y cantos</x:v>
       </x:c>
@@ -6706,14 +6839,14 @@
         <x:v>285600</x:v>
       </x:c>
       <x:c r="G14" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D14),ISNUMBER(F14)),D14*F14,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D14),ISNUMBER(F14)),D14*F14,"Por cotizar")</x:f>
         <x:v>285600</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>Necesario 181 m: 149,2 m netos + 5 cm por borde (306 bordes) + 10 %. Sobran unos 19 m para cantear en el armado las piezas pequeñas que no acepte la máquina.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="28.799999237060547">
+        <x:v>Necesario 186 m: 152,6 m netos + 5 cm por borde (318 bordes) + 10 %. Sobran unos 14 m para cantear en el armado las piezas pequeñas que no acepte la máquina.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
       <x:c r="A15" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6731,7 +6864,7 @@
         <x:v>41215</x:v>
       </x:c>
       <x:c r="G15" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D15),ISNUMBER(F15)),D15*F15,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D15),ISNUMBER(F15)),D15*F15,"Por cotizar")</x:f>
         <x:v>41215</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
@@ -6756,14 +6889,14 @@
         <x:v>51014</x:v>
       </x:c>
       <x:c r="G16" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D16),ISNUMBER(F16)),D16*F16,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D16),ISNUMBER(F16)),D16*F16,"Por cotizar")</x:f>
         <x:v>51014</x:v>
       </x:c>
       <x:c r="H16" s="17" t="str">
         <x:v>Tramos B3 670 + B4 400 = 1070 mm. Una barra de 3 m; remates y mecanizados por validar.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="28.799999237060547">
+    <x:row r="17">
       <x:c r="A17" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6781,14 +6914,14 @@
         <x:v>47034</x:v>
       </x:c>
       <x:c r="G17" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D17),ISNUMBER(F17)),D17*F17,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D17),ISNUMBER(F17)),D17*F17,"Por cotizar")</x:f>
         <x:v>47034</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
         <x:v>Solo cajón cubiertero B3. Vano 640 − 27 = caja 613; interior 583 × 520. Precio previo 47.034 COP/par. B4 lleva plataforma RH sin paredes encima y otro par HRE126-55.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="43.20000076293945">
+    <x:row r="18">
       <x:c r="A18" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6806,7 +6939,7 @@
         <x:v>63539</x:v>
       </x:c>
       <x:c r="G18" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D18),ISNUMBER(F18)),D18*F18,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D18),ISNUMBER(F18)),D18*F18,"Por cotizar")</x:f>
         <x:v>63539</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
@@ -6831,7 +6964,7 @@
         <x:v>38791</x:v>
       </x:c>
       <x:c r="G19" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D19),ISNUMBER(F19)),D19*F19,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D19),ISNUMBER(F19)),D19*F19,"Por cotizar")</x:f>
         <x:v>38791</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
@@ -6856,14 +6989,14 @@
         <x:v>2042</x:v>
       </x:c>
       <x:c r="G20" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D20),ISNUMBER(F20)),D20*F20,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D20),ISNUMBER(F20)),D20*F20,"Por cotizar")</x:f>
         <x:v>49008</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
         <x:v>Cinco módulos bajos: 20 apoyos básicos + 4 refuerzos por distribuir según cargas. Madecentro.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="28.799999237060547">
+    <x:row r="21">
       <x:c r="A21" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6881,14 +7014,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G21" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D21),ISNUMBER(F21)),D21*F21,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D21),ISNUMBER(F21)),D21*F21,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
         <x:v>Uno por gabinete superior (S1–S5). Verificar cabida en S1 (luz 165) y riel mural compatible; sin listones a 45° definidos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="43.20000076293945">
+    <x:row r="22">
       <x:c r="A22" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6906,14 +7039,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G22" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D22),ISNUMBER(F22)),D22*F22,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D22),ISNUMBER(F22)),D22*F22,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
-        <x:v>24 soportes de entrepaño (6 entrepaños × 4: S1, dos en S3, S5, B3 y B5). Tornillos de armado 4 × 50 (≈150) y de herrajes 4 × 16 (≈150), cantidad preliminar; no duplicar los 12 que trae cada par de rieles. Fijaciones de fondos y anclajes según muro real.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="72">
+        <x:v>24 soportes de entrepaño. Añadir cuatro escuadras compatibles para P075/P076 y cuatro fijaciones de campana según plantilla/fabricante; no duplicar tornillos incluidos en rieles. Unir apoyos a costados y P047; no depender sólo de tornillos al canto. Dos topes de apertura 90° para B4 superior/S5 y anclajes según muro real. Por cotizar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
       <x:c r="A23" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6931,14 +7064,14 @@
         <x:v>122902</x:v>
       </x:c>
       <x:c r="G23" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D23),ISNUMBER(F23)),D23*F23,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D23),ISNUMBER(F23)),D23*F23,"Por cotizar")</x:f>
         <x:v>122902</x:v>
       </x:c>
       <x:c r="H23" s="17" t="str">
         <x:v>Precio aportado por usuario 26/10/2026. Módulo nominal 150 × 500 × 600, herraje 100 × 446 × 470; con rieles laterales el conjunto mide 135 mm (medido por el usuario), por eso B1 es de 180 exterior (150 libres). Incluye rieles y enganches; no comprar otro par. https://madecentro.com/products/canasta-condimentero-tres-niveles-gris-antracita-cierre-lento-copia</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="57.599998474121094">
+    <x:row r="24">
       <x:c r="A24" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6956,14 +7089,14 @@
         <x:v>109700</x:v>
       </x:c>
       <x:c r="G24" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D24),ISNUMBER(F24)),D24*F24,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D24),ISNUMBER(F24)),D24*F24,"Por cotizar")</x:f>
         <x:v>109700</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
         <x:v>Precio aportado por usuario 26/10/2026. Herraje 485 × 330 × 215, módulo nominal 400. NO incluye sistema extraíble. https://madecentro.com/collections/herrajes-para-cocina/products/hso688-00-basureras-y-estructura-plastica-gris-de-12l-2-basureas-330x485x215mm-para-modulo-de-400</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="57.599998474121094">
+    <x:row r="25">
       <x:c r="A25" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -6981,14 +7114,14 @@
         <x:v>12560</x:v>
       </x:c>
       <x:c r="G25" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D25),ISNUMBER(F25)),D25*F25,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D25),ISNUMBER(F25)),D25*F25,"Por cotizar")</x:f>
         <x:v>12560</x:v>
       </x:c>
       <x:c r="H25" s="17" t="str">
         <x:v>Precio consultado 26/10/2026 para variante 55 cm. Incluye par y 12 tornillos. Montaje lateral VERTICAL en largueros inferiores, no acostado. Descuento de ancho, altura y perforación pendientes de ficha HRE126. https://madecentro.com/products/riel-corredera-para-cajon-de-extension-total-carga-media-38-kg?variant=45720301699302</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="28.799999237060547">
+    <x:row r="26">
       <x:c r="A26" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7006,14 +7139,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G26" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D26),ISNUMBER(F26)),D26*F26,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D26),ISNUMBER(F26)),D26*F26,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H26" s="17" t="str">
         <x:v>Sistema para 5 gabinetes; S1 luz 165. Dimensionar anclajes según farol/muro real, carga y fabricante. No hay suspensión de bajos a 45°.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="57.599998474121094">
+    <x:row r="27">
       <x:c r="A27" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7031,14 +7164,14 @@
         <x:v>9126</x:v>
       </x:c>
       <x:c r="G27" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D27),ISNUMBER(F27)),D27*F27,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D27),ISNUMBER(F27)),D27*F27,"Por cotizar")</x:f>
         <x:v>18252</x:v>
       </x:c>
       <x:c r="H27" s="17" t="str">
-        <x:v>2 por módulo de 600; 9.126 COP/unidad aportados por usuario 26/10/2026. Incluye platinas y tornillos; requiere bisagras (dos superiores ya previstas, sin duplicarlas). Fuerza y montaje a validar con peso real de puerta; 2,07 kg es aproximación del usuario. https://madecentro.com/products/hec060-03-brazo-neumatico-cierre-lento-60n</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="57.599998474121094">
+        <x:v>Previsión de dos brazos en módulo exterior de 600 mm. Puerta RH15 de 447 × 597, ≈2,7 kg; RESELECCIONAR fuerza con tabla de altura/peso y disposición de dos brazos. HEC060-03/60 N y precio previo 9.126 COP/u son provisionales, no compra validada. Bisagras y cotas de montaje por confirmar. https://madecentro.com/products/hec060-03-brazo-neumatico-cierre-lento-60n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
       <x:c r="A28" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7056,14 +7189,14 @@
         <x:v>2998</x:v>
       </x:c>
       <x:c r="G28" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D28),ISNUMBER(F28)),D28*F28,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D28),ISNUMBER(F28)),D28*F28,"Por cotizar")</x:f>
         <x:v>29980</x:v>
       </x:c>
       <x:c r="H28" s="17" t="str">
         <x:v>8 extremos de cuatro tramos + 2 apoyos intermedios en superior de 1770 mm. Previsión de diseño, no separación certificada. Precio de referencia Mobile: confirmar compatibilidad con gola comprada antes de comprar/mecanizar. https://madecentro.com/products/escuadra-para-perfil-gola-peralm63-64</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="28.799999237060547">
+    <x:row r="29">
       <x:c r="A29" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7083,14 +7216,14 @@
         <x:v>11287</x:v>
       </x:c>
       <x:c r="G29" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D29),ISNUMBER(F29)),D29*F29,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D29),ISNUMBER(F29)),D29*F29,"Por cotizar")</x:f>
         <x:v>33861</x:v>
       </x:c>
       <x:c r="H29" s="17" t="str">
         <x:v>Vano 830 − 27 = caja 803 × 450. Los 45 kg nominales del par no certifican la caja ni la carga útil. Incluye 12 tornillos de 12 mm por par. Confirmar uniones.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="57.599998474121094">
+    <x:row r="30">
       <x:c r="A30" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7110,14 +7243,14 @@
         <x:v>12730</x:v>
       </x:c>
       <x:c r="G30" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D30),ISNUMBER(F30)),D30*F30,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D30),ISNUMBER(F30)),D30*F30,"Por cotizar")</x:f>
         <x:v>12730</x:v>
       </x:c>
       <x:c r="H30" s="17" t="str">
         <x:v>Kit publicado: 4 rodamientos, 1 guía, 1 tope y tornillos. Identificar si coinciden con la guía y el amortiguador descritos por el usuario, antes de añadir accesorios. Cada hoja RH pesa 21,3 kg sin herrajes (10,05 kg/m², dato de Madecentro); el kit indica 30 kg: preguntar si es por hoja o por kit de dos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="57.599998474121094">
+    <x:row r="31">
       <x:c r="A31" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7137,14 +7270,14 @@
         <x:v>33278</x:v>
       </x:c>
       <x:c r="G31" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D31),ISNUMBER(F31)),D31*F31,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D31),ISNUMBER(F31)),D31*F31,"Por cotizar")</x:f>
         <x:v>33278</x:v>
       </x:c>
       <x:c r="H31" s="17" t="str">
         <x:v>Barra 2 m para recorrido 1920 mm. Referencia real: zona de 70 mm de fondo, hojas entre 500 y 550 mm, cuerpo hasta 560. El riel se atornilla al listón de pino del bastidor (no a la tapa). Guía inferior sin apoyo de peso; no hay riel inferior de carga. Confirmar sección y taladros del sistema.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="43.20000076293945">
+    <x:row r="32">
       <x:c r="A32" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7164,14 +7297,14 @@
         <x:v>2743</x:v>
       </x:c>
       <x:c r="G32" s="19" t="n">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D32),ISNUMBER(F32)),D32*F32,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D32),ISNUMBER(F32)),D32*F32,"Por cotizar")</x:f>
         <x:v>5486</x:v>
       </x:c>
       <x:c r="H32" s="17" t="str">
         <x:v>Una manija vertical en el extremo exterior de cada hoja.35 mm de saliente: fondo máximo 585 mm. Dos centros 96 mm; largo representado 119 mm. Las manijas no sustituyen una certificación de rigidez del tablero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="43.20000076293945">
+    <x:row r="33">
       <x:c r="A33" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7186,14 +7319,14 @@
       </x:c>
       <x:c r="F33" s="9"/>
       <x:c r="G33" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D33),ISNUMBER(F33)),D33*F33,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D33),ISNUMBER(F33)),D33*F33,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H33" s="17" t="str">
         <x:v>Detrás de la hoja exterior, conserva 50 mm de desfase y evita invertir el orden de hojas. Cota de pérdida de recorrido aportada por el usuario. Verificar si viene en el kit; no duplicar compra. La guía inferior tampoco se compra dos veces.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="28.799999237060547">
+    <x:row r="34">
       <x:c r="A34" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7211,7 +7344,7 @@
       </x:c>
       <x:c r="F34" s="9"/>
       <x:c r="G34" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D34),ISNUMBER(F34)),D34*F34,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D34),ISNUMBER(F34)),D34*F34,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H34" s="17" t="str">
@@ -7236,14 +7369,14 @@
       </x:c>
       <x:c r="F35" s="9"/>
       <x:c r="G35" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D35),ISNUMBER(F35)),D35*F35,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D35),ISNUMBER(F35)),D35*F35,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H35" s="17" t="str">
         <x:v>Dos por barra. Fijación y carga para RH15 por confirmar.</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="28.799999237060547">
+    <x:row r="36">
       <x:c r="A36" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7261,14 +7394,14 @@
       </x:c>
       <x:c r="F36" s="9"/>
       <x:c r="G36" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D36),ISNUMBER(F36)),D36*F36,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D36),ISNUMBER(F36)),D36*F36,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
         <x:v>Dos bajo cada lateral/divisor. El modelo dibuja 20 mm de apoyo y base total 100 mm; producto y regulación por elegir.</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="43.20000076293945">
+    <x:row r="37">
       <x:c r="A37" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7286,14 +7419,14 @@
       </x:c>
       <x:c r="F37" s="9"/>
       <x:c r="G37" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D37),ISNUMBER(F37)),D37*F37,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D37),ISNUMBER(F37)),D37*F37,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
         <x:v>Unir el marco completo C3-025 a C3-030 a laterales, divisor, pisos y tapas. Dimensionar anclajes al muro posterior resistente y al izquierdo. No fijar solo al estuco. El lateral derecho queda libre: el montante se une a la caja y al muro de fondo, no a una pared lateral inexistente. El marco abierto no se da por equivalente a un panel arriostrante.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="72">
+    <x:row r="38">
       <x:c r="A38" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7311,14 +7444,14 @@
       </x:c>
       <x:c r="F38" s="9"/>
       <x:c r="G38" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D38),ISNUMBER(F38)),D38*F38,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D38),ISNUMBER(F38)),D38*F38,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
         <x:v>Listón de pino de 4×4 cm que va de lateral a lateral: 1920 mm libres más el encaje en cada lateral (máx. 7 mm por lado). Pedir de 2,0 m o más, recto, seco y sin nudos grandes; sobra para 2 tacos de 15 mm. Va encajonado y atornillado a los laterales; el riel (50 mm) se atornilla a su cara inferior y sobresale ~5 mm por lado. El clóset real usa 7×3 cm; se cambió a 4×4 por disponibilidad. Confirmar rebaje y tornillos con el instalador.</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="28.799999237060547">
+    <x:row r="39">
       <x:c r="A39" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7336,7 +7469,7 @@
       </x:c>
       <x:c r="F39" s="9"/>
       <x:c r="G39" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D39),ISNUMBER(F39)),D39*F39,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D39),ISNUMBER(F39)),D39*F39,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H39" s="17" t="str">
@@ -7361,7 +7494,7 @@
       </x:c>
       <x:c r="F40" s="9"/>
       <x:c r="G40" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D40),ISNUMBER(F40)),D40*F40,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D40),ISNUMBER(F40)),D40*F40,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H40" s="17" t="str">
@@ -7386,7 +7519,7 @@
       </x:c>
       <x:c r="F41" s="9"/>
       <x:c r="G41" s="19" t="str">
-        <x:f t="shared" si="0">IF(AND(ISNUMBER(D41),ISNUMBER(F41)),D41*F41,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D41),ISNUMBER(F41)),D41*F41,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H41" s="17" t="str">
@@ -7411,14 +7544,14 @@
       </x:c>
       <x:c r="F42" s="9"/>
       <x:c r="G42" s="19" t="str">
-        <x:f t="shared" ref="G42:G60" si="1">IF(AND(ISNUMBER(D42),ISNUMBER(F42)),D42*F42,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D42),ISNUMBER(F42)),D42*F42,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H42" s="17" t="str">
         <x:v>Productos compatibles con RH, canto, piedra y espejo según aplicación.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="28.799999237060547">
+    <x:row r="43">
       <x:c r="A43" s="13" t="str">
         <x:v>Herrajes</x:v>
       </x:c>
@@ -7438,14 +7571,14 @@
         <x:v>17750</x:v>
       </x:c>
       <x:c r="G43" s="19" t="n">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D43),ISNUMBER(F43)),D43*F43,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D43),ISNUMBER(F43)),D43*F43,"Por cotizar")</x:f>
         <x:v>266250</x:v>
       </x:c>
       <x:c r="H43" s="17" t="str">
         <x:v>Cocina 12 pares (24 bisagras) + baño 3 pares (6 bisagras). Validar peso y cabida en el gabinete del espejo.</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="72">
+    <x:row r="44">
       <x:c r="A44" s="13" t="str">
         <x:v>Mesón, equipos y grifería</x:v>
       </x:c>
@@ -7463,14 +7596,14 @@
         <x:v>1486300</x:v>
       </x:c>
       <x:c r="G44" s="19" t="n">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D44),ISNUMBER(F44)),D44*F44,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D44),ISNUMBER(F44)),D44*F44,"Por cotizar")</x:f>
         <x:v>1486300</x:v>
       </x:c>
       <x:c r="H44" s="17" t="str">
         <x:v>Placa de 15 mm confirmada por usuario y ficha Homecenter. Precio $1.486.300 conservado. Recortes, material final, apoyos y posible borde engrosado por definir. La ficha mezcla 260/150 cm y granito/cuarzo: confirmar suministro concreto. https://www.homecenter.com.co/homecenter-co/product/519014/meson-granito-natural-crema-marfil-260-cm-x-62-cm/519014/</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="86.4000015258789">
+    <x:row r="45">
       <x:c r="A45" s="13" t="str">
         <x:v>Mesón, equipos y grifería</x:v>
       </x:c>
@@ -7488,14 +7621,14 @@
         <x:v>209900</x:v>
       </x:c>
       <x:c r="G45" s="19" t="n">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D45),ISNUMBER(F45)),D45*F45,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D45),ISNUMBER(F45)),D45*F45,"Por cotizar")</x:f>
         <x:v>209900</x:v>
       </x:c>
       <x:c r="H45" s="17" t="str">
         <x:v>Socoda AS350 satinado, código 87730: $209.900 conservados. 550 × 430 EXTERIORES, profundidad 165 mm. Abertura interior 490 × 370 según ficha descrita por usuario. Submontar: pestaña bajo placa, con anclaje/soporte compatibles. Hueco de corte lo define plantilla Socoda y acabado del borde; 490 × 370 solo referencia 3D. https://www.homecenter.com.co/homecenter-co/product/87730/lavaplatos-de-submontar-1-poceta-55x43-cm-acero-inoxidable-socoda/87730/</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="28.799999237060547">
+    <x:row r="46">
       <x:c r="A46" s="13" t="str">
         <x:v>Mesón, equipos y grifería</x:v>
       </x:c>
@@ -7513,7 +7646,7 @@
         <x:v>1864800</x:v>
       </x:c>
       <x:c r="G46" s="19" t="n">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D46),ISNUMBER(F46)),D46*F46,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D46),ISNUMBER(F46)),D46*F46,"Por cotizar")</x:f>
         <x:v>1864800</x:v>
       </x:c>
       <x:c r="H46" s="17" t="str">
@@ -7538,7 +7671,7 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G47" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D47),ISNUMBER(F47)),D47*F47,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D47),ISNUMBER(F47)),D47*F47,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H47" s="17" t="str">
@@ -7563,19 +7696,19 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G48" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D48),ISNUMBER(F48)),D48*F48,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D48),ISNUMBER(F48)),D48*F48,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H48" s="17" t="str">
         <x:v>Sifón y llaves deben permitir retirar el entrepaño del B5. No incluye canasta bajo fregadero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="28.799999237060547">
+    <x:row r="49">
       <x:c r="A49" s="13" t="str">
         <x:v>Mesón, equipos y grifería</x:v>
       </x:c>
       <x:c r="B49" s="13" t="str">
-        <x:v>Ducto y accesorios de campana</x:v>
+        <x:v>Instalación de campana Tofu · recirculación</x:v>
       </x:c>
       <x:c r="C49" s="13" t="str">
         <x:v>Cocina</x:v>
@@ -7588,14 +7721,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G49" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D49),ISNUMBER(F49)),D49*F49,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D49),ISNUMBER(F49)),D49*F49,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H49" s="17" t="str">
-        <x:v>Definir según modelo Haceb, diámetro y salida. Perforar el piso P047 (y el techo P046 si sale hacia arriba) según manual.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="28.799999237060547">
+        <x:v>CAMP TOFU 60 V3 NE: sistema recirculador según Haceb, con salidas de aire libres. No perforar P047/P046 para un ducto supuesto. Definir soporte mecánico del modelo exacto y seguir su ficha; no admite anclaje directo a pared. Ficha Haceb 9002650 rev.00: https://firplak.com/wp-content/uploads/2024/05/Campana-TOFU-60-V3-NEGRO.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
       <x:c r="A50" s="13" t="str">
         <x:v>Mesón, equipos y grifería</x:v>
       </x:c>
@@ -7613,7 +7746,7 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G50" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D50),ISNUMBER(F50)),D50*F50,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D50),ISNUMBER(F50)),D50*F50,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H50" s="17" t="str">
@@ -7638,7 +7771,7 @@
       </x:c>
       <x:c r="F51" s="9"/>
       <x:c r="G51" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D51),ISNUMBER(F51)),D51*F51,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D51),ISNUMBER(F51)),D51*F51,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H51" s="17" t="str">
@@ -7663,7 +7796,7 @@
       </x:c>
       <x:c r="F52" s="9"/>
       <x:c r="G52" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D52),ISNUMBER(F52)),D52*F52,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D52),ISNUMBER(F52)),D52*F52,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H52" s="17" t="str">
@@ -7688,7 +7821,7 @@
       </x:c>
       <x:c r="F53" s="9"/>
       <x:c r="G53" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D53),ISNUMBER(F53)),D53*F53,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D53),ISNUMBER(F53)),D53*F53,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H53" s="17" t="str">
@@ -7713,7 +7846,7 @@
       </x:c>
       <x:c r="F54" s="9"/>
       <x:c r="G54" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D54),ISNUMBER(F54)),D54*F54,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D54),ISNUMBER(F54)),D54*F54,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H54" s="17" t="str">
@@ -7738,14 +7871,14 @@
       </x:c>
       <x:c r="F55" s="9"/>
       <x:c r="G55" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D55),ISNUMBER(F55)),D55*F55,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D55),ISNUMBER(F55)),D55*F55,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H55" s="17" t="str">
         <x:v>Vuelos 15 mm a los lados y 5 mm delante; recortes según equipos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="28.799999237060547">
+    <x:row r="56">
       <x:c r="A56" s="13" t="str">
         <x:v>Accesorios</x:v>
       </x:c>
@@ -7763,14 +7896,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G56" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D56),ISNUMBER(F56)),D56*F56,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D56),ISNUMBER(F56)),D56*F56,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H56" s="17" t="str">
         <x:v>Zona derecha de 40 cm; dibujo ilustrativo 375 × 400, confirmar modelo. Escribir 0 solo si ya se tiene y se reutiliza.</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="57.599998474121094">
+    <x:row r="57">
       <x:c r="A57" s="13" t="str">
         <x:v>Servicios</x:v>
       </x:c>
@@ -7788,14 +7921,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G57" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D57),ISNUMBER(F57)),D57*F57,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D57),ISNUMBER(F57)),D57*F57,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H57" s="17" t="str">
         <x:v>Plantillas y recortes en placa 15 mm. Lavaplatos 550 × 430 exterior NO es medida de hueco; referencia 3D 490 × 370, plantilla Socoda y tipo de borde mandan. Profundidad 165. Marmolero define radios, tolerancias, apoyos y anclajes; recorte estufa sigue por manual. Borde engrosado opcional por cotizar.</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="28.799999237060547">
+    <x:row r="58">
       <x:c r="A58" s="13" t="str">
         <x:v>Servicios</x:v>
       </x:c>
@@ -7813,7 +7946,7 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G58" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D58),ISNUMBER(F58)),D58*F58,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D58),ISNUMBER(F58)),D58*F58,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H58" s="17" t="str">
@@ -7838,14 +7971,14 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G59" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D59),ISNUMBER(F59)),D59*F59,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D59),ISNUMBER(F59)),D59*F59,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H59" s="17" t="str">
         <x:v>Ingresar 0 únicamente si se confirma incluido.</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="28.799999237060547">
+    <x:row r="60">
       <x:c r="A60" s="13" t="str">
         <x:v>Servicios</x:v>
       </x:c>
@@ -7865,7 +7998,7 @@
         <x:v>cotizar</x:v>
       </x:c>
       <x:c r="G60" s="19" t="str">
-        <x:f t="shared" si="1">IF(AND(ISNUMBER(D60),ISNUMBER(F60)),D60*F60,"Por cotizar")</x:f>
+        <x:f>IF(AND(ISNUMBER(D60),ISNUMBER(F60)),D60*F60,"Por cotizar")</x:f>
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="H60" s="17" t="str">
@@ -7951,14 +8084,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="10" customWidth="1"/>
+    <x:col min="1" max="1" width="10" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
     <x:col min="3" max="3" width="40" customWidth="1"/>
     <x:col min="4" max="4" width="100" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Antes de cortar</x:v>
       </x:c>
@@ -7982,7 +8116,7 @@
         <x:v>Qué falta</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="28.799999237060547">
+    <x:row r="7" ht="90" customHeight="1">
       <x:c r="A7" s="17" t="str">
         <x:v>Clóset</x:v>
       </x:c>
@@ -7995,6 +8129,12 @@
       <x:c r="D7" s="17" t="str">
         <x:v>Confirmar en obra que el eje de la puerta de la habitación está a 2880 mm del muro izquierdo: el ancho de 1950 depende de esa cota (2880 − 900 − 10 − 20).</x:v>
       </x:c>
+    </x:row>
+    <x:row r="8" ht="160" customHeight="1">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="23"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8003,14 +8143,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.399999618530273"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="10" customWidth="1"/>
+    <x:col min="1" max="1" width="10" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
     <x:col min="3" max="3" width="40" customWidth="1"/>
     <x:col min="4" max="4" width="110" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" ht="18">
+    <x:row r="2">
       <x:c r="A2" s="10" t="str">
         <x:v>Lo que se corta, recorta o rebaja en el armado</x:v>
       </x:c>
@@ -8048,7 +8189,7 @@
         <x:v>Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="28.799999237060547">
+    <x:row r="8">
       <x:c r="A8" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8059,7 +8200,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -8076,7 +8217,7 @@
         <x:v>Su altura se fija en el armado según el manual del horno; si pide más ventilación atrás, recortar el borde trasero (sin canto).</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="28.799999237060547">
+    <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8104,7 +8245,7 @@
         <x:v>Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="28.799999237060547">
+    <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8115,7 +8256,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -8132,7 +8273,7 @@
         <x:v>Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="28.799999237060547">
+    <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8143,7 +8284,7 @@
         <x:v>Travesaño de canto</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8174,7 +8315,7 @@
         <x:v>Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="28.799999237060547">
+    <x:row r="17">
       <x:c r="A17" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8185,7 +8326,7 @@
         <x:v>Travesaño horizontal</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8202,7 +8343,7 @@
         <x:v>Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="28.799999237060547">
+    <x:row r="19">
       <x:c r="A19" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8216,7 +8357,7 @@
         <x:v>NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="28.799999237060547">
+    <x:row r="20">
       <x:c r="A20" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8227,10 +8368,10 @@
         <x:v>PROVISIONAL larguero bajo plataforma basurero</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 549,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="28.799999237060547">
+        <x:v>Si no la cantean: cortar a 549.1 × 59.1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
       <x:c r="A21" s="17" t="str">
         <x:v>Cocina</x:v>
       </x:c>
@@ -8241,62 +8382,76 @@
         <x:v>PROVISIONAL travesaño bajo plataforma basurero</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>Si no la cantean: cortar a 312,1 × 59,1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
+        <x:v>Si no la cantean: cortar a 312.1 × 59.1 y cantear en el armado. NO PEDIR: se corta en el armado de un sobrante, con el riel HRE126-55 y la bandeja en mano. Pedir a la sucursal que entregue los sobrantes.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="17" t="str">
-        <x:v>Clóset</x:v>
+        <x:v>Cocina</x:v>
       </x:c>
       <x:c r="B22" s="17" t="str">
-        <x:v>C3-001</x:v>
+        <x:v>P071</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>Lateral exterior</x:v>
+        <x:v>Faja retranqueada de agarre sobre campana (de un retal)</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>Rebaje superior para el listón de pino 4 × 4 en taller.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="28.799999237060547">
+        <x:v>Si no la cantean: cortar a 569.1 × 59.1 y cantear en el armado. NO PEDIR: se corta en el armado de un retal (570 × 60) y se cantea con flexible 0,45 mm en los cuatro bordes. Pedir a la sucursal que entregue los sobrantes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
       <x:c r="A23" s="17" t="str">
         <x:v>Clóset</x:v>
       </x:c>
       <x:c r="B23" s="17" t="str">
+        <x:v>C3-001</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="str">
+        <x:v>Lateral exterior</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>Rebaje superior para el listón de pino 4 × 4 en taller.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="17" t="str">
+        <x:v>Clóset</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="str">
         <x:v>C3-023</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="str">
+      <x:c r="C24" s="17" t="str">
         <x:v>Hoja corrediza RH15</x:v>
       </x:c>
-      <x:c r="D23" s="17" t="str">
+      <x:c r="D24" s="17" t="str">
         <x:v>Pedida 20 mm más alta (2195 en vez de 2175): en el armado, con el riel y los carros puestos, recortar el borde superior —tapado por la solapa— hasta que la guía inferior sujete la hoja. Nunca debe quedar corta.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="28.799999237060547">
-      <x:c r="A24" s="17" t="str">
-        <x:v>Baño</x:v>
-      </x:c>
-      <x:c r="B24" s="17" t="str">
-        <x:v>B03</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="str">
-        <x:v>Entrepaño retranqueado con reserva de sifón</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="57.599998474121094">
+    <x:row r="25">
       <x:c r="A25" s="17" t="str">
         <x:v>Baño</x:v>
       </x:c>
       <x:c r="B25" s="17" t="str">
+        <x:v>B03</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="str">
+        <x:v>Entrepaño retranqueado con reserva de sifón</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="17" t="str">
+        <x:v>Baño</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="str">
         <x:v>B06</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="str">
+      <x:c r="C26" s="17" t="str">
         <x:v>Panel común para dos puertas: corte diagonal en armado</x:v>
       </x:c>
-      <x:c r="D25" s="17" t="str">
+      <x:c r="D26" s="17" t="str">
         <x:v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</x:v>
       </x:c>
     </x:row>
